--- a/Result/checksun/塑膠工業.xlsx
+++ b/Result/checksun/塑膠工業.xlsx
@@ -1013,7 +1013,11 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr"/>
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -1301,7 +1305,11 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B4" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -1589,7 +1597,11 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B5" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -1877,7 +1889,11 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B6" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -2165,7 +2181,11 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B7" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -2453,7 +2473,11 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B8" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -2741,7 +2765,11 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B9" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -3029,7 +3057,11 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr"/>
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B10" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -3317,7 +3349,11 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr"/>
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B11" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -3605,7 +3641,11 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B12" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -4185,7 +4225,11 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B14" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -4473,7 +4517,11 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr"/>
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B15" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -4761,7 +4809,11 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr"/>
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B16" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -5049,7 +5101,11 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B17" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -5337,7 +5393,11 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr"/>
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B18" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -5625,7 +5685,11 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B19" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -5913,7 +5977,11 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr"/>
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B20" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -6201,7 +6269,11 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr"/>
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B21" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -6489,7 +6561,11 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr"/>
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B22" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -6777,7 +6853,11 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr"/>
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B23" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -7357,7 +7437,11 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr"/>
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B25" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -7645,7 +7729,11 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B26" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -7933,7 +8021,11 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr"/>
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B27" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -8221,7 +8313,11 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr"/>
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B28" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -8509,7 +8605,11 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr"/>
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B29" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -8797,7 +8897,11 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr"/>
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B30" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -9085,7 +9189,11 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" t="inlineStr"/>
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B31" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -9373,7 +9481,11 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" t="inlineStr"/>
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B32" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -9661,7 +9773,11 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="inlineStr"/>
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B33" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -9949,7 +10065,11 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" t="inlineStr"/>
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B34" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -10529,7 +10649,11 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" t="inlineStr"/>
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B36" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -10817,7 +10941,11 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" t="inlineStr"/>
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B37" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -11105,7 +11233,11 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="inlineStr"/>
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B38" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -11393,7 +11525,11 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" t="inlineStr"/>
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B39" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -11681,7 +11817,11 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" t="inlineStr"/>
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B40" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -11969,7 +12109,11 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" t="inlineStr"/>
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B41" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -12257,7 +12401,11 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="inlineStr"/>
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B42" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -12545,7 +12693,11 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" t="inlineStr"/>
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B43" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -12833,7 +12985,11 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" t="inlineStr"/>
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B44" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -13121,7 +13277,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" t="inlineStr"/>
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B45" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -13701,7 +13861,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr"/>
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B47" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -13989,7 +14153,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" t="inlineStr"/>
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B48" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -14277,7 +14445,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B49" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -14565,7 +14737,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr"/>
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B50" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -14853,7 +15029,11 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" t="inlineStr"/>
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B51" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -15141,7 +15321,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" t="inlineStr"/>
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B52" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -15429,7 +15613,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" t="inlineStr"/>
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B53" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -15717,7 +15905,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" t="inlineStr"/>
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B54" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -16005,7 +16197,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" t="inlineStr"/>
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B55" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -16293,7 +16489,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" t="inlineStr"/>
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B56" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -16873,7 +17073,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" t="inlineStr"/>
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B58" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -17161,7 +17365,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" t="inlineStr"/>
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B59" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -17449,7 +17657,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" t="inlineStr"/>
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B60" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -17737,7 +17949,11 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" t="inlineStr"/>
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B61" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -18025,7 +18241,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" t="inlineStr"/>
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B62" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -18313,7 +18533,11 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" t="inlineStr"/>
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B63" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -18601,7 +18825,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" t="inlineStr"/>
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B64" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -18889,7 +19117,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" t="inlineStr"/>
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B65" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -19177,7 +19409,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" t="inlineStr"/>
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B66" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -19465,7 +19701,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" t="inlineStr"/>
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B67" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -20045,7 +20285,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" t="inlineStr"/>
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B69" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -20333,7 +20577,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" t="inlineStr"/>
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B70" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -20621,7 +20869,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" t="inlineStr"/>
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B71" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -20909,7 +21161,11 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" t="inlineStr"/>
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B72" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -21197,7 +21453,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" t="inlineStr"/>
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B73" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -21485,7 +21745,11 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" t="inlineStr"/>
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B74" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -21773,7 +22037,11 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" t="inlineStr"/>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B75" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -22061,7 +22329,11 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="inlineStr"/>
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B76" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -22349,7 +22621,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" t="inlineStr"/>
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B77" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -22637,7 +22913,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" t="inlineStr"/>
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B78" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -23217,7 +23497,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" t="inlineStr"/>
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B80" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -23505,7 +23789,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" t="inlineStr"/>
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B81" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -23793,7 +24081,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" t="inlineStr"/>
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B82" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -24081,7 +24373,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" t="inlineStr"/>
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B83" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -24369,7 +24665,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" t="inlineStr"/>
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B84" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -24657,7 +24957,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" t="inlineStr"/>
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B85" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -24945,7 +25249,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" t="inlineStr"/>
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B86" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -25233,7 +25541,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" t="inlineStr"/>
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B87" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -25521,7 +25833,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="inlineStr"/>
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B88" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -25809,7 +26125,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" t="inlineStr"/>
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B89" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -26389,7 +26709,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" t="inlineStr"/>
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B91" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -26677,7 +27001,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" t="inlineStr"/>
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B92" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -26965,7 +27293,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" t="inlineStr"/>
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B93" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -27253,7 +27585,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" t="inlineStr"/>
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B94" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -27541,7 +27877,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr"/>
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B95" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -27829,7 +28169,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr"/>
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B96" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -28117,7 +28461,11 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" t="inlineStr"/>
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B97" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -28405,7 +28753,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B98" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -28693,7 +29045,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" t="inlineStr"/>
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B99" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -28981,7 +29337,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" t="inlineStr"/>
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B100" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -29561,7 +29921,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" t="inlineStr"/>
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B102" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -29849,7 +30213,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" t="inlineStr"/>
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B103" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -30137,7 +30505,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" t="inlineStr"/>
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B104" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -30425,7 +30797,11 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B105" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -30713,7 +31089,11 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" t="inlineStr"/>
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B106" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -31001,7 +31381,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" t="inlineStr"/>
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B107" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -31289,7 +31673,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr"/>
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B108" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -31577,7 +31965,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" t="inlineStr"/>
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B109" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -31865,7 +32257,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" t="inlineStr"/>
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B110" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -32153,7 +32549,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" t="inlineStr"/>
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B111" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -32733,7 +33133,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" t="inlineStr"/>
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B113" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -33021,7 +33425,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B114" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -33309,7 +33717,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" t="inlineStr"/>
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B115" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -33597,7 +34009,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" t="inlineStr"/>
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B116" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -33885,7 +34301,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr"/>
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B117" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -34173,7 +34593,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="inlineStr"/>
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B118" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -34461,7 +34885,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" t="inlineStr"/>
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B119" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -34749,7 +35177,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" t="inlineStr"/>
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B120" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -35037,7 +35469,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" t="inlineStr"/>
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B121" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -35325,7 +35761,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="inlineStr"/>
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B122" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -35905,7 +36345,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" t="inlineStr"/>
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B124" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -36193,7 +36637,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" t="inlineStr"/>
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B125" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -36481,7 +36929,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" t="inlineStr"/>
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B126" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -36769,7 +37221,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" t="inlineStr"/>
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B127" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -37057,7 +37513,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" t="inlineStr"/>
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B128" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -37345,7 +37805,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" t="inlineStr"/>
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B129" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -37633,7 +38097,11 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" t="inlineStr"/>
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B130" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -37921,7 +38389,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" t="inlineStr"/>
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B131" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -38209,7 +38681,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" t="inlineStr"/>
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B132" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -38497,7 +38973,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr"/>
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B133" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -39077,7 +39557,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B135" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -39365,7 +39849,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" t="inlineStr"/>
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B136" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -39653,7 +40141,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" t="inlineStr"/>
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B137" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -39941,7 +40433,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr"/>
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B138" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -40229,7 +40725,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" t="inlineStr"/>
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B139" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -40517,7 +41017,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" t="inlineStr"/>
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B140" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -40805,7 +41309,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" t="inlineStr"/>
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B141" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -41093,7 +41601,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr"/>
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B142" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -41381,7 +41893,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" t="inlineStr"/>
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B143" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -41669,7 +42185,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B144" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -42249,7 +42769,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" t="inlineStr"/>
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B146" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -42537,7 +43061,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr"/>
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B147" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -42825,7 +43353,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" t="inlineStr"/>
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B148" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -43113,7 +43645,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" t="inlineStr"/>
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B149" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -43401,7 +43937,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" t="inlineStr"/>
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B150" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -43689,7 +44229,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr"/>
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B151" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -43977,7 +44521,11 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" t="inlineStr"/>
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B152" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -44265,7 +44813,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" t="inlineStr"/>
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B153" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -44553,7 +45105,11 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" t="inlineStr"/>
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B154" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -44841,7 +45397,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr"/>
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B155" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -45421,7 +45981,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" t="inlineStr"/>
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B157" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -45709,7 +46273,11 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" t="inlineStr"/>
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B158" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -45997,7 +46565,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr"/>
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B159" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -46285,7 +46857,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" t="inlineStr"/>
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B160" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -46573,7 +47149,11 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" t="inlineStr"/>
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B161" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -46861,7 +47441,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" t="inlineStr"/>
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B162" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -47149,7 +47733,11 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr"/>
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B163" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -47437,7 +48025,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" t="inlineStr"/>
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B164" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -47725,7 +48317,11 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" t="inlineStr"/>
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B165" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -48013,7 +48609,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" t="inlineStr"/>
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B166" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -48301,7 +48901,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" t="inlineStr"/>
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B167" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -48589,7 +49193,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" t="inlineStr"/>
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B168" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -48877,7 +49485,11 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" t="inlineStr"/>
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B169" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -49165,7 +49777,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" t="inlineStr"/>
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B170" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -49453,7 +50069,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" t="inlineStr"/>
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B171" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -50033,7 +50653,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr"/>
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B173" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -50321,7 +50945,11 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" t="inlineStr"/>
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B174" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -50609,7 +51237,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" t="inlineStr"/>
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B175" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -50897,7 +51529,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr"/>
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B176" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -51185,7 +51821,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" t="inlineStr"/>
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B177" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -51473,7 +52113,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B178" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -51761,7 +52405,11 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" t="inlineStr"/>
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B179" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -52049,7 +52697,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr"/>
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B180" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -52337,7 +52989,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" t="inlineStr"/>
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B181" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -52625,7 +53281,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" t="inlineStr"/>
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B182" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -53205,7 +53865,11 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr"/>
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B184" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -53493,7 +54157,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" t="inlineStr"/>
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B185" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -53781,7 +54449,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" t="inlineStr"/>
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B186" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -54069,7 +54741,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr"/>
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B187" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -54357,7 +55033,11 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" t="inlineStr"/>
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B188" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -54645,7 +55325,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" t="inlineStr"/>
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B189" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -54933,7 +55617,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" t="inlineStr"/>
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B190" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -55221,7 +55909,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr"/>
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B191" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -55509,7 +56201,11 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" t="inlineStr"/>
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B192" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -55797,7 +56493,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B193" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -56377,7 +57077,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" t="inlineStr"/>
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B195" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -56665,7 +57369,11 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B196" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -56953,7 +57661,11 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" t="inlineStr"/>
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B197" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -57241,7 +57953,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" t="inlineStr"/>
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B198" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -57529,7 +58245,11 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" t="inlineStr"/>
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B199" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -57817,7 +58537,11 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" t="inlineStr"/>
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B200" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -58105,7 +58829,11 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B201" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -58393,7 +59121,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" t="inlineStr"/>
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B202" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -58681,7 +59413,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B203" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -58969,7 +59705,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" t="inlineStr"/>
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B204" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -59549,7 +60289,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" t="inlineStr"/>
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B206" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -59837,7 +60581,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr"/>
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B207" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -60125,7 +60873,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" t="inlineStr"/>
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B208" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -60413,7 +61165,11 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr"/>
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B209" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -60701,7 +61457,11 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" t="inlineStr"/>
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B210" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -60989,7 +61749,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" t="inlineStr"/>
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B211" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -61277,7 +62041,11 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B212" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -61565,7 +62333,11 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" t="inlineStr"/>
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B213" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -61853,7 +62625,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr"/>
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B214" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -62141,7 +62917,11 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" t="inlineStr"/>
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B215" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -62721,7 +63501,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" t="inlineStr"/>
+      <c r="A217" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B217" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -63009,7 +63793,11 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" t="inlineStr"/>
+      <c r="A218" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B218" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -63297,7 +64085,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" t="inlineStr"/>
+      <c r="A219" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B219" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -63585,7 +64377,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" t="inlineStr"/>
+      <c r="A220" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B220" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -63873,7 +64669,11 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" t="inlineStr"/>
+      <c r="A221" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B221" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -64161,7 +64961,11 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" t="inlineStr"/>
+      <c r="A222" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B222" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -64449,7 +65253,11 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" t="inlineStr"/>
+      <c r="A223" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B223" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -64737,7 +65545,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" t="inlineStr"/>
+      <c r="A224" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B224" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -65025,7 +65837,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
+      <c r="A225" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B225" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -65313,7 +66129,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" t="inlineStr"/>
+      <c r="A226" t="inlineStr">
+        <is>
+          <t>【d】</t>
+        </is>
+      </c>
       <c r="B226" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -65893,7 +66713,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" t="inlineStr"/>
+      <c r="A228" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B228" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -66181,7 +67005,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
+      <c r="A229" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B229" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -66469,7 +67297,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" t="inlineStr"/>
+      <c r="A230" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B230" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -66757,7 +67589,11 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" t="inlineStr"/>
+      <c r="A231" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B231" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -67045,7 +67881,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" t="inlineStr"/>
+      <c r="A232" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B232" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -67333,7 +68173,11 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" t="inlineStr"/>
+      <c r="A233" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B233" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -67621,7 +68465,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" t="inlineStr"/>
+      <c r="A234" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B234" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -67909,7 +68757,11 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" t="inlineStr"/>
+      <c r="A235" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B235" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -68197,7 +69049,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" t="inlineStr"/>
+      <c r="A236" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B236" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -68485,7 +69341,11 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" t="inlineStr"/>
+      <c r="A237" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B237" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -69065,7 +69925,11 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" t="inlineStr"/>
+      <c r="A239" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B239" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -69353,7 +70217,11 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" t="inlineStr"/>
+      <c r="A240" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B240" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -69641,7 +70509,11 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr"/>
+      <c r="A241" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B241" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -69929,7 +70801,11 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" t="inlineStr"/>
+      <c r="A242" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B242" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -70217,7 +71093,11 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" t="inlineStr"/>
+      <c r="A243" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B243" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -70505,7 +71385,11 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" t="inlineStr"/>
+      <c r="A244" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B244" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -70793,7 +71677,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" t="inlineStr"/>
+      <c r="A245" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B245" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -71081,7 +71969,11 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr"/>
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B246" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -71369,7 +72261,11 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" t="inlineStr"/>
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B247" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -71657,7 +72553,11 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr"/>
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B248" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -72237,7 +73137,11 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" t="inlineStr"/>
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B250" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -72525,7 +73429,11 @@
       </c>
     </row>
     <row r="251">
-      <c r="A251" t="inlineStr"/>
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B251" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -72813,7 +73721,11 @@
       </c>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr"/>
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B252" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -73101,7 +74013,11 @@
       </c>
     </row>
     <row r="253">
-      <c r="A253" t="inlineStr"/>
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B253" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -73389,7 +74305,11 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr"/>
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B254" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -73677,7 +74597,11 @@
       </c>
     </row>
     <row r="255">
-      <c r="A255" t="inlineStr"/>
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B255" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -73965,7 +74889,11 @@
       </c>
     </row>
     <row r="256">
-      <c r="A256" t="inlineStr"/>
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B256" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -74253,7 +75181,11 @@
       </c>
     </row>
     <row r="257">
-      <c r="A257" t="inlineStr"/>
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B257" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -74541,7 +75473,11 @@
       </c>
     </row>
     <row r="258">
-      <c r="A258" t="inlineStr"/>
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B258" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -74829,7 +75765,11 @@
       </c>
     </row>
     <row r="259">
-      <c r="A259" t="inlineStr"/>
+      <c r="A259" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B259" t="inlineStr">
         <is>
           <t>2025-08-25</t>
@@ -75409,7 +76349,11 @@
       </c>
     </row>
     <row r="261">
-      <c r="A261" t="inlineStr"/>
+      <c r="A261" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B261" t="inlineStr">
         <is>
           <t>2025-09-05</t>
@@ -75697,7 +76641,11 @@
       </c>
     </row>
     <row r="262">
-      <c r="A262" t="inlineStr"/>
+      <c r="A262" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B262" t="inlineStr">
         <is>
           <t>2025-09-04</t>
@@ -75985,7 +76933,11 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" t="inlineStr"/>
+      <c r="A263" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B263" t="inlineStr">
         <is>
           <t>2025-09-03</t>
@@ -76273,7 +77225,11 @@
       </c>
     </row>
     <row r="264">
-      <c r="A264" t="inlineStr"/>
+      <c r="A264" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B264" t="inlineStr">
         <is>
           <t>2025-09-02</t>
@@ -76561,7 +77517,11 @@
       </c>
     </row>
     <row r="265">
-      <c r="A265" t="inlineStr"/>
+      <c r="A265" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B265" t="inlineStr">
         <is>
           <t>2025-09-01</t>
@@ -76849,7 +77809,11 @@
       </c>
     </row>
     <row r="266">
-      <c r="A266" t="inlineStr"/>
+      <c r="A266" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B266" t="inlineStr">
         <is>
           <t>2025-08-29</t>
@@ -77137,7 +78101,11 @@
       </c>
     </row>
     <row r="267">
-      <c r="A267" t="inlineStr"/>
+      <c r="A267" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B267" t="inlineStr">
         <is>
           <t>2025-08-28</t>
@@ -77425,7 +78393,11 @@
       </c>
     </row>
     <row r="268">
-      <c r="A268" t="inlineStr"/>
+      <c r="A268" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B268" t="inlineStr">
         <is>
           <t>2025-08-27</t>
@@ -77713,7 +78685,11 @@
       </c>
     </row>
     <row r="269">
-      <c r="A269" t="inlineStr"/>
+      <c r="A269" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B269" t="inlineStr">
         <is>
           <t>2025-08-26</t>
@@ -78001,7 +78977,11 @@
       </c>
     </row>
     <row r="270">
-      <c r="A270" t="inlineStr"/>
+      <c r="A270" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
       <c r="B270" t="inlineStr">
         <is>
           <t>2025-08-25</t>

--- a/Result/checksun/塑膠工業.xlsx
+++ b/Result/checksun/塑膠工業.xlsx
@@ -1011,15 +1011,11 @@
           <t>13.6325</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>14.258</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>14.785</t>
-        </is>
+      <c r="AN2" t="n">
+        <v>14.258</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>14.785</v>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
@@ -1398,15 +1394,11 @@
           <t>13.6775</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>14.315</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>14.81625</t>
-        </is>
+      <c r="AN3" t="n">
+        <v>14.315</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>14.81625</v>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
@@ -1785,15 +1777,11 @@
           <t>13.715</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>14.366</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>14.848125</t>
-        </is>
+      <c r="AN4" t="n">
+        <v>14.366</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>14.848125</v>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
@@ -2172,15 +2160,11 @@
           <t>13.7475</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>14.413</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>14.88</t>
-        </is>
+      <c r="AN5" t="n">
+        <v>14.413</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>14.88</v>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
@@ -2559,15 +2543,11 @@
           <t>13.7775</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>14.457</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>14.910625</t>
-        </is>
+      <c r="AN6" t="n">
+        <v>14.457</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>14.910625</v>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
@@ -2946,15 +2926,11 @@
           <t>13.7975</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>14.491</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>14.936875</t>
-        </is>
+      <c r="AN7" t="n">
+        <v>14.491</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>14.936875</v>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
@@ -3333,15 +3309,11 @@
           <t>13.8175</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>14.525</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>14.963125</t>
-        </is>
+      <c r="AN8" t="n">
+        <v>14.525</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>14.963125</v>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
@@ -3720,15 +3692,11 @@
           <t>13.8275</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>14.558</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>14.990625</t>
-        </is>
+      <c r="AN9" t="n">
+        <v>14.558</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>14.990625</v>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
@@ -4107,15 +4075,11 @@
           <t>13.85</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>14.597</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>15.01875</t>
-        </is>
+      <c r="AN10" t="n">
+        <v>14.597</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>15.01875</v>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
@@ -4494,15 +4458,11 @@
           <t>13.865</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>14.637</t>
-        </is>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>15.045</t>
-        </is>
+      <c r="AN11" t="n">
+        <v>14.637</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>15.045</v>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
@@ -4881,15 +4841,11 @@
           <t>41.1475</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>40.9</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>42.490625</t>
-        </is>
+      <c r="AN12" t="n">
+        <v>40.9</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>42.490625</v>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
@@ -5268,15 +5224,11 @@
           <t>41.1275</t>
         </is>
       </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>40.89100000000001</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>42.55125</t>
-        </is>
+      <c r="AN13" t="n">
+        <v>40.89100000000001</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>42.55125</v>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
@@ -5655,15 +5607,11 @@
           <t>41.1075</t>
         </is>
       </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>40.887</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>42.605</t>
-        </is>
+      <c r="AN14" t="n">
+        <v>40.887</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>42.605</v>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
@@ -6042,15 +5990,11 @@
           <t>41.08499999999999</t>
         </is>
       </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>40.89</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>42.660625</t>
-        </is>
+      <c r="AN15" t="n">
+        <v>40.89</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>42.660625</v>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
@@ -6429,15 +6373,11 @@
           <t>41.0825</t>
         </is>
       </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>40.873</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>42.714375</t>
-        </is>
+      <c r="AN16" t="n">
+        <v>40.873</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>42.714375</v>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
@@ -6816,15 +6756,11 @@
           <t>41.08</t>
         </is>
       </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>40.862</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>42.770625</t>
-        </is>
+      <c r="AN17" t="n">
+        <v>40.862</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>42.770625</v>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
@@ -7203,15 +7139,11 @@
           <t>41.0825</t>
         </is>
       </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>40.858</t>
-        </is>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>42.8225</t>
-        </is>
+      <c r="AN18" t="n">
+        <v>40.858</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>42.8225</v>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
@@ -7590,15 +7522,11 @@
           <t>41.07</t>
         </is>
       </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>40.92</t>
-        </is>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>42.875</t>
-        </is>
+      <c r="AN19" t="n">
+        <v>40.92</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>42.875</v>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
@@ -7977,15 +7905,11 @@
           <t>41.06</t>
         </is>
       </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>40.988</t>
-        </is>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>42.936875</t>
-        </is>
+      <c r="AN20" t="n">
+        <v>40.988</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>42.936875</v>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
@@ -8364,15 +8288,11 @@
           <t>41.065</t>
         </is>
       </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>41.067</t>
-        </is>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>43.0025</t>
-        </is>
+      <c r="AN21" t="n">
+        <v>41.067</v>
+      </c>
+      <c r="AO21" t="n">
+        <v>43.0025</v>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
@@ -8751,15 +8671,11 @@
           <t>11.1295</t>
         </is>
       </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>9.4978</t>
-        </is>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>9.584875</t>
-        </is>
+      <c r="AN22" t="n">
+        <v>9.4978</v>
+      </c>
+      <c r="AO22" t="n">
+        <v>9.584875</v>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
@@ -9138,15 +9054,11 @@
           <t>10.6445</t>
         </is>
       </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>9.3198</t>
-        </is>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>9.48675</t>
-        </is>
+      <c r="AN23" t="n">
+        <v>9.319800000000001</v>
+      </c>
+      <c r="AO23" t="n">
+        <v>9.486750000000001</v>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
@@ -9525,15 +9437,11 @@
           <t>10.2395</t>
         </is>
       </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>9.1722</t>
-        </is>
-      </c>
-      <c r="AO24" t="inlineStr">
-        <is>
-          <t>9.411125000000002</t>
-        </is>
+      <c r="AN24" t="n">
+        <v>9.1722</v>
+      </c>
+      <c r="AO24" t="n">
+        <v>9.411125000000002</v>
       </c>
       <c r="AP24" t="inlineStr">
         <is>
@@ -9912,15 +9820,11 @@
           <t>9.915</t>
         </is>
       </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>9.053199999999999</t>
-        </is>
-      </c>
-      <c r="AO25" t="inlineStr">
-        <is>
-          <t>9.353625</t>
-        </is>
+      <c r="AN25" t="n">
+        <v>9.0532</v>
+      </c>
+      <c r="AO25" t="n">
+        <v>9.353624999999999</v>
       </c>
       <c r="AP25" t="inlineStr">
         <is>
@@ -10299,15 +10203,11 @@
           <t>9.658</t>
         </is>
       </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>8.9612</t>
-        </is>
-      </c>
-      <c r="AO26" t="inlineStr">
-        <is>
-          <t>9.31175</t>
-        </is>
+      <c r="AN26" t="n">
+        <v>8.9612</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>9.31175</v>
       </c>
       <c r="AP26" t="inlineStr">
         <is>
@@ -10686,15 +10586,11 @@
           <t>9.411</t>
         </is>
       </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>8.8728</t>
-        </is>
-      </c>
-      <c r="AO27" t="inlineStr">
-        <is>
-          <t>9.272375</t>
-        </is>
+      <c r="AN27" t="n">
+        <v>8.8728</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>9.272375</v>
       </c>
       <c r="AP27" t="inlineStr">
         <is>
@@ -11073,15 +10969,11 @@
           <t>9.224</t>
         </is>
       </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>8.7936</t>
-        </is>
-      </c>
-      <c r="AO28" t="inlineStr">
-        <is>
-          <t>9.248625</t>
-        </is>
+      <c r="AN28" t="n">
+        <v>8.7936</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>9.248625000000001</v>
       </c>
       <c r="AP28" t="inlineStr">
         <is>
@@ -11460,15 +11352,11 @@
           <t>9.0345</t>
         </is>
       </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>8.7286</t>
-        </is>
-      </c>
-      <c r="AO29" t="inlineStr">
-        <is>
-          <t>9.224875</t>
-        </is>
+      <c r="AN29" t="n">
+        <v>8.7286</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>9.224875000000001</v>
       </c>
       <c r="AP29" t="inlineStr">
         <is>
@@ -11847,15 +11735,11 @@
           <t>8.897499999999999</t>
         </is>
       </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>8.6846</t>
-        </is>
-      </c>
-      <c r="AO30" t="inlineStr">
-        <is>
-          <t>9.214875000000001</t>
-        </is>
+      <c r="AN30" t="n">
+        <v>8.6846</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>9.214874999999999</v>
       </c>
       <c r="AP30" t="inlineStr">
         <is>
@@ -12234,15 +12118,11 @@
           <t>8.778</t>
         </is>
       </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>8.6476</t>
-        </is>
-      </c>
-      <c r="AO31" t="inlineStr">
-        <is>
-          <t>9.208625000000001</t>
-        </is>
+      <c r="AN31" t="n">
+        <v>8.647600000000001</v>
+      </c>
+      <c r="AO31" t="n">
+        <v>9.208625</v>
       </c>
       <c r="AP31" t="inlineStr">
         <is>
@@ -12621,15 +12501,11 @@
           <t>72.585</t>
         </is>
       </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>74.31599999999999</t>
-        </is>
-      </c>
-      <c r="AO32" t="inlineStr">
-        <is>
-          <t>77.075</t>
-        </is>
+      <c r="AN32" t="n">
+        <v>74.31599999999999</v>
+      </c>
+      <c r="AO32" t="n">
+        <v>77.075</v>
       </c>
       <c r="AP32" t="inlineStr">
         <is>
@@ -13008,15 +12884,11 @@
           <t>72.74000000000001</t>
         </is>
       </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>74.498</t>
-        </is>
-      </c>
-      <c r="AO33" t="inlineStr">
-        <is>
-          <t>77.10249999999999</t>
-        </is>
+      <c r="AN33" t="n">
+        <v>74.498</v>
+      </c>
+      <c r="AO33" t="n">
+        <v>77.10249999999999</v>
       </c>
       <c r="AP33" t="inlineStr">
         <is>
@@ -13395,15 +13267,11 @@
           <t>72.845</t>
         </is>
       </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>74.726</t>
-        </is>
-      </c>
-      <c r="AO34" t="inlineStr">
-        <is>
-          <t>77.125</t>
-        </is>
+      <c r="AN34" t="n">
+        <v>74.726</v>
+      </c>
+      <c r="AO34" t="n">
+        <v>77.125</v>
       </c>
       <c r="AP34" t="inlineStr">
         <is>
@@ -13782,15 +13650,11 @@
           <t>72.965</t>
         </is>
       </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>74.916</t>
-        </is>
-      </c>
-      <c r="AO35" t="inlineStr">
-        <is>
-          <t>77.16499999999999</t>
-        </is>
+      <c r="AN35" t="n">
+        <v>74.916</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>77.16499999999999</v>
       </c>
       <c r="AP35" t="inlineStr">
         <is>
@@ -14169,15 +14033,11 @@
           <t>73.015</t>
         </is>
       </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>75.102</t>
-        </is>
-      </c>
-      <c r="AO36" t="inlineStr">
-        <is>
-          <t>77.20500000000001</t>
-        </is>
+      <c r="AN36" t="n">
+        <v>75.102</v>
+      </c>
+      <c r="AO36" t="n">
+        <v>77.20500000000001</v>
       </c>
       <c r="AP36" t="inlineStr">
         <is>
@@ -14556,15 +14416,11 @@
           <t>73.095</t>
         </is>
       </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>75.266</t>
-        </is>
-      </c>
-      <c r="AO37" t="inlineStr">
-        <is>
-          <t>77.23125</t>
-        </is>
+      <c r="AN37" t="n">
+        <v>75.26600000000001</v>
+      </c>
+      <c r="AO37" t="n">
+        <v>77.23125</v>
       </c>
       <c r="AP37" t="inlineStr">
         <is>
@@ -14943,15 +14799,11 @@
           <t>73.13499999999999</t>
         </is>
       </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>75.476</t>
-        </is>
-      </c>
-      <c r="AO38" t="inlineStr">
-        <is>
-          <t>77.2775</t>
-        </is>
+      <c r="AN38" t="n">
+        <v>75.476</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>77.2775</v>
       </c>
       <c r="AP38" t="inlineStr">
         <is>
@@ -15330,15 +15182,11 @@
           <t>72.975</t>
         </is>
       </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>75.63600000000001</t>
-        </is>
-      </c>
-      <c r="AO39" t="inlineStr">
-        <is>
-          <t>77.31500000000001</t>
-        </is>
+      <c r="AN39" t="n">
+        <v>75.63600000000001</v>
+      </c>
+      <c r="AO39" t="n">
+        <v>77.31500000000001</v>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
@@ -15717,15 +15565,11 @@
           <t>72.93499999999999</t>
         </is>
       </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>75.8</t>
-        </is>
-      </c>
-      <c r="AO40" t="inlineStr">
-        <is>
-          <t>77.32624999999999</t>
-        </is>
+      <c r="AN40" t="n">
+        <v>75.8</v>
+      </c>
+      <c r="AO40" t="n">
+        <v>77.32624999999999</v>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
@@ -16104,15 +15948,11 @@
           <t>72.82000000000001</t>
         </is>
       </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>75.93799999999999</t>
-        </is>
-      </c>
-      <c r="AO41" t="inlineStr">
-        <is>
-          <t>77.33</t>
-        </is>
+      <c r="AN41" t="n">
+        <v>75.93799999999999</v>
+      </c>
+      <c r="AO41" t="n">
+        <v>77.33</v>
       </c>
       <c r="AP41" t="inlineStr">
         <is>
@@ -16491,15 +16331,11 @@
           <t>58.88500000000001</t>
         </is>
       </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>60.214</t>
-        </is>
-      </c>
-      <c r="AO42" t="inlineStr">
-        <is>
-          <t>62.17625</t>
-        </is>
+      <c r="AN42" t="n">
+        <v>60.214</v>
+      </c>
+      <c r="AO42" t="n">
+        <v>62.17625</v>
       </c>
       <c r="AP42" t="inlineStr">
         <is>
@@ -16878,15 +16714,11 @@
           <t>58.89</t>
         </is>
       </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>60.32</t>
-        </is>
-      </c>
-      <c r="AO43" t="inlineStr">
-        <is>
-          <t>62.265</t>
-        </is>
+      <c r="AN43" t="n">
+        <v>60.32</v>
+      </c>
+      <c r="AO43" t="n">
+        <v>62.265</v>
       </c>
       <c r="AP43" t="inlineStr">
         <is>
@@ -17265,15 +17097,11 @@
           <t>58.96999999999999</t>
         </is>
       </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>60.45399999999999</t>
-        </is>
-      </c>
-      <c r="AO44" t="inlineStr">
-        <is>
-          <t>62.3725</t>
-        </is>
+      <c r="AN44" t="n">
+        <v>60.45399999999999</v>
+      </c>
+      <c r="AO44" t="n">
+        <v>62.3725</v>
       </c>
       <c r="AP44" t="inlineStr">
         <is>
@@ -17652,15 +17480,11 @@
           <t>58.98999999999999</t>
         </is>
       </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>60.532</t>
-        </is>
-      </c>
-      <c r="AO45" t="inlineStr">
-        <is>
-          <t>62.46</t>
-        </is>
+      <c r="AN45" t="n">
+        <v>60.532</v>
+      </c>
+      <c r="AO45" t="n">
+        <v>62.46</v>
       </c>
       <c r="AP45" t="inlineStr">
         <is>
@@ -18039,15 +17863,11 @@
           <t>58.94499999999999</t>
         </is>
       </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>60.582</t>
-        </is>
-      </c>
-      <c r="AO46" t="inlineStr">
-        <is>
-          <t>62.52624999999999</t>
-        </is>
+      <c r="AN46" t="n">
+        <v>60.582</v>
+      </c>
+      <c r="AO46" t="n">
+        <v>62.52624999999999</v>
       </c>
       <c r="AP46" t="inlineStr">
         <is>
@@ -18426,15 +18246,11 @@
           <t>58.815</t>
         </is>
       </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>60.624</t>
-        </is>
-      </c>
-      <c r="AO47" t="inlineStr">
-        <is>
-          <t>62.59499999999999</t>
-        </is>
+      <c r="AN47" t="n">
+        <v>60.624</v>
+      </c>
+      <c r="AO47" t="n">
+        <v>62.59499999999999</v>
       </c>
       <c r="AP47" t="inlineStr">
         <is>
@@ -18813,15 +18629,11 @@
           <t>58.815</t>
         </is>
       </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>60.692</t>
-        </is>
-      </c>
-      <c r="AO48" t="inlineStr">
-        <is>
-          <t>62.65124999999999</t>
-        </is>
+      <c r="AN48" t="n">
+        <v>60.692</v>
+      </c>
+      <c r="AO48" t="n">
+        <v>62.65124999999999</v>
       </c>
       <c r="AP48" t="inlineStr">
         <is>
@@ -19200,15 +19012,11 @@
           <t>58.84</t>
         </is>
       </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>60.792</t>
-        </is>
-      </c>
-      <c r="AO49" t="inlineStr">
-        <is>
-          <t>62.76125</t>
-        </is>
+      <c r="AN49" t="n">
+        <v>60.792</v>
+      </c>
+      <c r="AO49" t="n">
+        <v>62.76125</v>
       </c>
       <c r="AP49" t="inlineStr">
         <is>
@@ -19587,15 +19395,11 @@
           <t>58.965</t>
         </is>
       </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>60.94</t>
-        </is>
-      </c>
-      <c r="AO50" t="inlineStr">
-        <is>
-          <t>62.87375000000001</t>
-        </is>
+      <c r="AN50" t="n">
+        <v>60.94</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>62.87375000000001</v>
       </c>
       <c r="AP50" t="inlineStr">
         <is>
@@ -19974,15 +19778,11 @@
           <t>59.05</t>
         </is>
       </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>61.08799999999999</t>
-        </is>
-      </c>
-      <c r="AO51" t="inlineStr">
-        <is>
-          <t>62.95500000000001</t>
-        </is>
+      <c r="AN51" t="n">
+        <v>61.08799999999999</v>
+      </c>
+      <c r="AO51" t="n">
+        <v>62.95500000000001</v>
       </c>
       <c r="AP51" t="inlineStr">
         <is>
@@ -20361,15 +20161,11 @@
           <t>6.963499999999999</t>
         </is>
       </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>6.710199999999999</t>
-        </is>
-      </c>
-      <c r="AO52" t="inlineStr">
-        <is>
-          <t>6.5655</t>
-        </is>
+      <c r="AN52" t="n">
+        <v>6.710199999999999</v>
+      </c>
+      <c r="AO52" t="n">
+        <v>6.5655</v>
       </c>
       <c r="AP52" t="inlineStr">
         <is>
@@ -20748,15 +20544,11 @@
           <t>7.05</t>
         </is>
       </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>6.703200000000001</t>
-        </is>
-      </c>
-      <c r="AO53" t="inlineStr">
-        <is>
-          <t>6.563624999999999</t>
-        </is>
+      <c r="AN53" t="n">
+        <v>6.703200000000001</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>6.563624999999999</v>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
@@ -21135,15 +20927,11 @@
           <t>7.150500000000001</t>
         </is>
       </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>6.6972</t>
-        </is>
-      </c>
-      <c r="AO54" t="inlineStr">
-        <is>
-          <t>6.563624999999999</t>
-        </is>
+      <c r="AN54" t="n">
+        <v>6.6972</v>
+      </c>
+      <c r="AO54" t="n">
+        <v>6.563624999999999</v>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
@@ -21522,15 +21310,11 @@
           <t>7.241499999999999</t>
         </is>
       </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>6.6862</t>
-        </is>
-      </c>
-      <c r="AO55" t="inlineStr">
-        <is>
-          <t>6.564375</t>
-        </is>
+      <c r="AN55" t="n">
+        <v>6.6862</v>
+      </c>
+      <c r="AO55" t="n">
+        <v>6.564375</v>
       </c>
       <c r="AP55" t="inlineStr">
         <is>
@@ -21909,15 +21693,11 @@
           <t>7.342999999999999</t>
         </is>
       </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>6.677</t>
-        </is>
-      </c>
-      <c r="AO56" t="inlineStr">
-        <is>
-          <t>6.565</t>
-        </is>
+      <c r="AN56" t="n">
+        <v>6.677</v>
+      </c>
+      <c r="AO56" t="n">
+        <v>6.565</v>
       </c>
       <c r="AP56" t="inlineStr">
         <is>
@@ -22296,15 +22076,11 @@
           <t>7.4095</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>6.664200000000001</t>
-        </is>
-      </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>6.563250000000001</t>
-        </is>
+      <c r="AN57" t="n">
+        <v>6.664200000000001</v>
+      </c>
+      <c r="AO57" t="n">
+        <v>6.563250000000001</v>
       </c>
       <c r="AP57" t="inlineStr">
         <is>
@@ -22683,15 +22459,11 @@
           <t>7.464499999999999</t>
         </is>
       </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>6.6534</t>
-        </is>
-      </c>
-      <c r="AO58" t="inlineStr">
-        <is>
-          <t>6.560375000000001</t>
-        </is>
+      <c r="AN58" t="n">
+        <v>6.6534</v>
+      </c>
+      <c r="AO58" t="n">
+        <v>6.560375000000001</v>
       </c>
       <c r="AP58" t="inlineStr">
         <is>
@@ -23070,15 +22842,11 @@
           <t>7.4815</t>
         </is>
       </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>6.643199999999999</t>
-        </is>
-      </c>
-      <c r="AO59" t="inlineStr">
-        <is>
-          <t>6.559125</t>
-        </is>
+      <c r="AN59" t="n">
+        <v>6.643199999999999</v>
+      </c>
+      <c r="AO59" t="n">
+        <v>6.559125</v>
       </c>
       <c r="AP59" t="inlineStr">
         <is>
@@ -23457,15 +23225,11 @@
           <t>7.468999999999999</t>
         </is>
       </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>6.6344</t>
-        </is>
-      </c>
-      <c r="AO60" t="inlineStr">
-        <is>
-          <t>6.555624999999999</t>
-        </is>
+      <c r="AN60" t="n">
+        <v>6.6344</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>6.555624999999999</v>
       </c>
       <c r="AP60" t="inlineStr">
         <is>
@@ -23844,15 +23608,11 @@
           <t>7.4295</t>
         </is>
       </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>6.6266</t>
-        </is>
-      </c>
-      <c r="AO61" t="inlineStr">
-        <is>
-          <t>6.5515</t>
-        </is>
+      <c r="AN61" t="n">
+        <v>6.6266</v>
+      </c>
+      <c r="AO61" t="n">
+        <v>6.5515</v>
       </c>
       <c r="AP61" t="inlineStr">
         <is>
@@ -24231,15 +23991,11 @@
           <t>5.0555</t>
         </is>
       </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>5.127000000000001</t>
-        </is>
-      </c>
-      <c r="AO62" t="inlineStr">
-        <is>
-          <t>5.26</t>
-        </is>
+      <c r="AN62" t="n">
+        <v>5.127000000000001</v>
+      </c>
+      <c r="AO62" t="n">
+        <v>5.26</v>
       </c>
       <c r="AP62" t="inlineStr">
         <is>
@@ -24618,15 +24374,11 @@
           <t>5.0625</t>
         </is>
       </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>5.136</t>
-        </is>
-      </c>
-      <c r="AO63" t="inlineStr">
-        <is>
-          <t>5.264875</t>
-        </is>
+      <c r="AN63" t="n">
+        <v>5.136</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>5.264875</v>
       </c>
       <c r="AP63" t="inlineStr">
         <is>
@@ -25005,15 +24757,11 @@
           <t>5.065499999999999</t>
         </is>
       </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>5.1438</t>
-        </is>
-      </c>
-      <c r="AO64" t="inlineStr">
-        <is>
-          <t>5.26975</t>
-        </is>
+      <c r="AN64" t="n">
+        <v>5.1438</v>
+      </c>
+      <c r="AO64" t="n">
+        <v>5.26975</v>
       </c>
       <c r="AP64" t="inlineStr">
         <is>
@@ -25392,15 +25140,11 @@
           <t>5.066000000000001</t>
         </is>
       </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>5.151</t>
-        </is>
-      </c>
-      <c r="AO65" t="inlineStr">
-        <is>
-          <t>5.274749999999999</t>
-        </is>
+      <c r="AN65" t="n">
+        <v>5.151</v>
+      </c>
+      <c r="AO65" t="n">
+        <v>5.274749999999999</v>
       </c>
       <c r="AP65" t="inlineStr">
         <is>
@@ -25779,15 +25523,11 @@
           <t>5.064500000000001</t>
         </is>
       </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>5.1578</t>
-        </is>
-      </c>
-      <c r="AO66" t="inlineStr">
-        <is>
-          <t>5.27775</t>
-        </is>
+      <c r="AN66" t="n">
+        <v>5.1578</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>5.27775</v>
       </c>
       <c r="AP66" t="inlineStr">
         <is>
@@ -26166,15 +25906,11 @@
           <t>5.057</t>
         </is>
       </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>5.162999999999999</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>5.279375</t>
-        </is>
+      <c r="AN67" t="n">
+        <v>5.162999999999999</v>
+      </c>
+      <c r="AO67" t="n">
+        <v>5.279375</v>
       </c>
       <c r="AP67" t="inlineStr">
         <is>
@@ -26553,15 +26289,11 @@
           <t>5.052</t>
         </is>
       </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>5.1704</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>5.28125</t>
-        </is>
+      <c r="AN68" t="n">
+        <v>5.1704</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>5.28125</v>
       </c>
       <c r="AP68" t="inlineStr">
         <is>
@@ -26940,15 +26672,11 @@
           <t>5.048</t>
         </is>
       </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>5.1782</t>
-        </is>
-      </c>
-      <c r="AO69" t="inlineStr">
-        <is>
-          <t>5.28425</t>
-        </is>
+      <c r="AN69" t="n">
+        <v>5.1782</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>5.28425</v>
       </c>
       <c r="AP69" t="inlineStr">
         <is>
@@ -27327,15 +27055,11 @@
           <t>5.047</t>
         </is>
       </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>5.187</t>
-        </is>
-      </c>
-      <c r="AO70" t="inlineStr">
-        <is>
-          <t>5.288125</t>
-        </is>
+      <c r="AN70" t="n">
+        <v>5.187</v>
+      </c>
+      <c r="AO70" t="n">
+        <v>5.288125</v>
       </c>
       <c r="AP70" t="inlineStr">
         <is>
@@ -27714,15 +27438,11 @@
           <t>5.0455</t>
         </is>
       </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>5.195600000000001</t>
-        </is>
-      </c>
-      <c r="AO71" t="inlineStr">
-        <is>
-          <t>5.289625</t>
-        </is>
+      <c r="AN71" t="n">
+        <v>5.195600000000001</v>
+      </c>
+      <c r="AO71" t="n">
+        <v>5.289625</v>
       </c>
       <c r="AP71" t="inlineStr">
         <is>
@@ -28101,15 +27821,11 @@
           <t>29.4875</t>
         </is>
       </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>29.383</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>28.226875</t>
-        </is>
+      <c r="AN72" t="n">
+        <v>29.383</v>
+      </c>
+      <c r="AO72" t="n">
+        <v>28.226875</v>
       </c>
       <c r="AP72" t="inlineStr">
         <is>
@@ -28488,15 +28204,11 @@
           <t>29.515</t>
         </is>
       </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>29.394</t>
-        </is>
-      </c>
-      <c r="AO73" t="inlineStr">
-        <is>
-          <t>28.159375</t>
-        </is>
+      <c r="AN73" t="n">
+        <v>29.394</v>
+      </c>
+      <c r="AO73" t="n">
+        <v>28.159375</v>
       </c>
       <c r="AP73" t="inlineStr">
         <is>
@@ -28875,15 +28587,11 @@
           <t>29.47</t>
         </is>
       </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>29.38</t>
-        </is>
-      </c>
-      <c r="AO74" t="inlineStr">
-        <is>
-          <t>28.080625</t>
-        </is>
+      <c r="AN74" t="n">
+        <v>29.38</v>
+      </c>
+      <c r="AO74" t="n">
+        <v>28.080625</v>
       </c>
       <c r="AP74" t="inlineStr">
         <is>
@@ -29262,15 +28970,11 @@
           <t>29.4375</t>
         </is>
       </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>29.346</t>
-        </is>
-      </c>
-      <c r="AO75" t="inlineStr">
-        <is>
-          <t>27.998125</t>
-        </is>
+      <c r="AN75" t="n">
+        <v>29.346</v>
+      </c>
+      <c r="AO75" t="n">
+        <v>27.998125</v>
       </c>
       <c r="AP75" t="inlineStr">
         <is>
@@ -29649,15 +29353,11 @@
           <t>29.345</t>
         </is>
       </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>29.312</t>
-        </is>
-      </c>
-      <c r="AO76" t="inlineStr">
-        <is>
-          <t>27.90625</t>
-        </is>
+      <c r="AN76" t="n">
+        <v>29.312</v>
+      </c>
+      <c r="AO76" t="n">
+        <v>27.90625</v>
       </c>
       <c r="AP76" t="inlineStr">
         <is>
@@ -30036,15 +29736,11 @@
           <t>29.2575</t>
         </is>
       </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>29.282</t>
-        </is>
-      </c>
-      <c r="AO77" t="inlineStr">
-        <is>
-          <t>27.808125</t>
-        </is>
+      <c r="AN77" t="n">
+        <v>29.282</v>
+      </c>
+      <c r="AO77" t="n">
+        <v>27.808125</v>
       </c>
       <c r="AP77" t="inlineStr">
         <is>
@@ -30423,15 +30119,11 @@
           <t>29.1675</t>
         </is>
       </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>29.224</t>
-        </is>
-      </c>
-      <c r="AO78" t="inlineStr">
-        <is>
-          <t>27.708125</t>
-        </is>
+      <c r="AN78" t="n">
+        <v>29.224</v>
+      </c>
+      <c r="AO78" t="n">
+        <v>27.708125</v>
       </c>
       <c r="AP78" t="inlineStr">
         <is>
@@ -30810,15 +30502,11 @@
           <t>29.1075</t>
         </is>
       </c>
-      <c r="AN79" t="inlineStr">
-        <is>
-          <t>29.156</t>
-        </is>
-      </c>
-      <c r="AO79" t="inlineStr">
-        <is>
-          <t>27.625</t>
-        </is>
+      <c r="AN79" t="n">
+        <v>29.156</v>
+      </c>
+      <c r="AO79" t="n">
+        <v>27.625</v>
       </c>
       <c r="AP79" t="inlineStr">
         <is>
@@ -31197,15 +30885,11 @@
           <t>29.0575</t>
         </is>
       </c>
-      <c r="AN80" t="inlineStr">
-        <is>
-          <t>29.101</t>
-        </is>
-      </c>
-      <c r="AO80" t="inlineStr">
-        <is>
-          <t>27.54812500000001</t>
-        </is>
+      <c r="AN80" t="n">
+        <v>29.101</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>27.54812500000001</v>
       </c>
       <c r="AP80" t="inlineStr">
         <is>
@@ -31584,15 +31268,11 @@
           <t>29.005</t>
         </is>
       </c>
-      <c r="AN81" t="inlineStr">
-        <is>
-          <t>29.04</t>
-        </is>
-      </c>
-      <c r="AO81" t="inlineStr">
-        <is>
-          <t>27.460625</t>
-        </is>
+      <c r="AN81" t="n">
+        <v>29.04</v>
+      </c>
+      <c r="AO81" t="n">
+        <v>27.460625</v>
       </c>
       <c r="AP81" t="inlineStr">
         <is>
@@ -31971,15 +31651,11 @@
           <t>30.495</t>
         </is>
       </c>
-      <c r="AN82" t="inlineStr">
-        <is>
-          <t>29.529</t>
-        </is>
-      </c>
-      <c r="AO82" t="inlineStr">
-        <is>
-          <t>29.285</t>
-        </is>
+      <c r="AN82" t="n">
+        <v>29.529</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>29.285</v>
       </c>
       <c r="AP82" t="inlineStr">
         <is>
@@ -32358,15 +32034,11 @@
           <t>30.5425</t>
         </is>
       </c>
-      <c r="AN83" t="inlineStr">
-        <is>
-          <t>29.487</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>29.278125</t>
-        </is>
+      <c r="AN83" t="n">
+        <v>29.487</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>29.278125</v>
       </c>
       <c r="AP83" t="inlineStr">
         <is>
@@ -32745,15 +32417,11 @@
           <t>30.515</t>
         </is>
       </c>
-      <c r="AN84" t="inlineStr">
-        <is>
-          <t>29.447</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>29.27375</t>
-        </is>
+      <c r="AN84" t="n">
+        <v>29.447</v>
+      </c>
+      <c r="AO84" t="n">
+        <v>29.27375</v>
       </c>
       <c r="AP84" t="inlineStr">
         <is>
@@ -33132,15 +32800,11 @@
           <t>30.5</t>
         </is>
       </c>
-      <c r="AN85" t="inlineStr">
-        <is>
-          <t>29.413</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>29.281875</t>
-        </is>
+      <c r="AN85" t="n">
+        <v>29.413</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>29.281875</v>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
@@ -33519,15 +33183,11 @@
           <t>30.4725</t>
         </is>
       </c>
-      <c r="AN86" t="inlineStr">
-        <is>
-          <t>29.383</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>29.300625</t>
-        </is>
+      <c r="AN86" t="n">
+        <v>29.383</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>29.300625</v>
       </c>
       <c r="AP86" t="inlineStr">
         <is>
@@ -33906,15 +33566,11 @@
           <t>30.39249999999999</t>
         </is>
       </c>
-      <c r="AN87" t="inlineStr">
-        <is>
-          <t>29.341</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>29.309375</t>
-        </is>
+      <c r="AN87" t="n">
+        <v>29.341</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>29.309375</v>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
@@ -34293,15 +33949,11 @@
           <t>30.295</t>
         </is>
       </c>
-      <c r="AN88" t="inlineStr">
-        <is>
-          <t>29.29</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>29.31</t>
-        </is>
+      <c r="AN88" t="n">
+        <v>29.29</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>29.31</v>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
@@ -34680,15 +34332,11 @@
           <t>30.1875</t>
         </is>
       </c>
-      <c r="AN89" t="inlineStr">
-        <is>
-          <t>29.245</t>
-        </is>
-      </c>
-      <c r="AO89" t="inlineStr">
-        <is>
-          <t>29.305625</t>
-        </is>
+      <c r="AN89" t="n">
+        <v>29.245</v>
+      </c>
+      <c r="AO89" t="n">
+        <v>29.305625</v>
       </c>
       <c r="AP89" t="inlineStr">
         <is>
@@ -35067,15 +34715,11 @@
           <t>30.165</t>
         </is>
       </c>
-      <c r="AN90" t="inlineStr">
-        <is>
-          <t>29.228</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>29.315625</t>
-        </is>
+      <c r="AN90" t="n">
+        <v>29.228</v>
+      </c>
+      <c r="AO90" t="n">
+        <v>29.315625</v>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
@@ -35454,15 +35098,11 @@
           <t>30.15</t>
         </is>
       </c>
-      <c r="AN91" t="inlineStr">
-        <is>
-          <t>29.236</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>29.326875</t>
-        </is>
+      <c r="AN91" t="n">
+        <v>29.236</v>
+      </c>
+      <c r="AO91" t="n">
+        <v>29.326875</v>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
@@ -35841,15 +35481,11 @@
           <t>11.265</t>
         </is>
       </c>
-      <c r="AN92" t="inlineStr">
-        <is>
-          <t>11.105</t>
-        </is>
-      </c>
-      <c r="AO92" t="inlineStr">
-        <is>
-          <t>11.084375</t>
-        </is>
+      <c r="AN92" t="n">
+        <v>11.105</v>
+      </c>
+      <c r="AO92" t="n">
+        <v>11.084375</v>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
@@ -36228,15 +35864,11 @@
           <t>11.2475</t>
         </is>
       </c>
-      <c r="AN93" t="inlineStr">
-        <is>
-          <t>11.1</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>11.08</t>
-        </is>
+      <c r="AN93" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>11.08</v>
       </c>
       <c r="AP93" t="inlineStr">
         <is>
@@ -36615,15 +36247,11 @@
           <t>11.2375</t>
         </is>
       </c>
-      <c r="AN94" t="inlineStr">
-        <is>
-          <t>11.093</t>
-        </is>
-      </c>
-      <c r="AO94" t="inlineStr">
-        <is>
-          <t>11.075</t>
-        </is>
+      <c r="AN94" t="n">
+        <v>11.093</v>
+      </c>
+      <c r="AO94" t="n">
+        <v>11.075</v>
       </c>
       <c r="AP94" t="inlineStr">
         <is>
@@ -37002,15 +36630,11 @@
           <t>11.21</t>
         </is>
       </c>
-      <c r="AN95" t="inlineStr">
-        <is>
-          <t>11.075</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>11.065625</t>
-        </is>
+      <c r="AN95" t="n">
+        <v>11.075</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>11.065625</v>
       </c>
       <c r="AP95" t="inlineStr">
         <is>
@@ -37389,15 +37013,11 @@
           <t>11.1775</t>
         </is>
       </c>
-      <c r="AN96" t="inlineStr">
-        <is>
-          <t>11.055</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>11.054375</t>
-        </is>
+      <c r="AN96" t="n">
+        <v>11.055</v>
+      </c>
+      <c r="AO96" t="n">
+        <v>11.054375</v>
       </c>
       <c r="AP96" t="inlineStr">
         <is>
@@ -37776,15 +37396,11 @@
           <t>11.16</t>
         </is>
       </c>
-      <c r="AN97" t="inlineStr">
-        <is>
-          <t>11.044</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>11.0475</t>
-        </is>
+      <c r="AN97" t="n">
+        <v>11.044</v>
+      </c>
+      <c r="AO97" t="n">
+        <v>11.0475</v>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
@@ -38163,15 +37779,11 @@
           <t>11.125</t>
         </is>
       </c>
-      <c r="AN98" t="inlineStr">
-        <is>
-          <t>11.026</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>11.035</t>
-        </is>
+      <c r="AN98" t="n">
+        <v>11.026</v>
+      </c>
+      <c r="AO98" t="n">
+        <v>11.035</v>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
@@ -38550,15 +38162,11 @@
           <t>11.0625</t>
         </is>
       </c>
-      <c r="AN99" t="inlineStr">
-        <is>
-          <t>10.998</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>11.016875</t>
-        </is>
+      <c r="AN99" t="n">
+        <v>10.998</v>
+      </c>
+      <c r="AO99" t="n">
+        <v>11.016875</v>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
@@ -38937,15 +38545,11 @@
           <t>11.04</t>
         </is>
       </c>
-      <c r="AN100" t="inlineStr">
-        <is>
-          <t>10.994</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>11.011875</t>
-        </is>
+      <c r="AN100" t="n">
+        <v>10.994</v>
+      </c>
+      <c r="AO100" t="n">
+        <v>11.011875</v>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
@@ -39324,15 +38928,11 @@
           <t>11.0225</t>
         </is>
       </c>
-      <c r="AN101" t="inlineStr">
-        <is>
-          <t>10.997</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>11.00875</t>
-        </is>
+      <c r="AN101" t="n">
+        <v>10.997</v>
+      </c>
+      <c r="AO101" t="n">
+        <v>11.00875</v>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
@@ -39711,15 +39311,11 @@
           <t>19.7475</t>
         </is>
       </c>
-      <c r="AN102" t="inlineStr">
-        <is>
-          <t>19.746</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>19.75125</t>
-        </is>
+      <c r="AN102" t="n">
+        <v>19.746</v>
+      </c>
+      <c r="AO102" t="n">
+        <v>19.75125</v>
       </c>
       <c r="AP102" t="inlineStr">
         <is>
@@ -40098,15 +39694,11 @@
           <t>19.755</t>
         </is>
       </c>
-      <c r="AN103" t="inlineStr">
-        <is>
-          <t>19.747</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>19.75375</t>
-        </is>
+      <c r="AN103" t="n">
+        <v>19.747</v>
+      </c>
+      <c r="AO103" t="n">
+        <v>19.75375</v>
       </c>
       <c r="AP103" t="inlineStr">
         <is>
@@ -40485,15 +40077,11 @@
           <t>19.76</t>
         </is>
       </c>
-      <c r="AN104" t="inlineStr">
-        <is>
-          <t>19.747</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>19.7575</t>
-        </is>
+      <c r="AN104" t="n">
+        <v>19.747</v>
+      </c>
+      <c r="AO104" t="n">
+        <v>19.7575</v>
       </c>
       <c r="AP104" t="inlineStr">
         <is>
@@ -40872,15 +40460,11 @@
           <t>19.765</t>
         </is>
       </c>
-      <c r="AN105" t="inlineStr">
-        <is>
-          <t>19.748</t>
-        </is>
-      </c>
-      <c r="AO105" t="inlineStr">
-        <is>
-          <t>19.760625</t>
-        </is>
+      <c r="AN105" t="n">
+        <v>19.748</v>
+      </c>
+      <c r="AO105" t="n">
+        <v>19.760625</v>
       </c>
       <c r="AP105" t="inlineStr">
         <is>
@@ -41259,15 +40843,11 @@
           <t>19.77</t>
         </is>
       </c>
-      <c r="AN106" t="inlineStr">
-        <is>
-          <t>19.749</t>
-        </is>
-      </c>
-      <c r="AO106" t="inlineStr">
-        <is>
-          <t>19.76125</t>
-        </is>
+      <c r="AN106" t="n">
+        <v>19.749</v>
+      </c>
+      <c r="AO106" t="n">
+        <v>19.76125</v>
       </c>
       <c r="AP106" t="inlineStr">
         <is>
@@ -41646,15 +41226,11 @@
           <t>19.7725</t>
         </is>
       </c>
-      <c r="AN107" t="inlineStr">
-        <is>
-          <t>19.749</t>
-        </is>
-      </c>
-      <c r="AO107" t="inlineStr">
-        <is>
-          <t>19.760625</t>
-        </is>
+      <c r="AN107" t="n">
+        <v>19.749</v>
+      </c>
+      <c r="AO107" t="n">
+        <v>19.760625</v>
       </c>
       <c r="AP107" t="inlineStr">
         <is>
@@ -42033,15 +41609,11 @@
           <t>19.7725</t>
         </is>
       </c>
-      <c r="AN108" t="inlineStr">
-        <is>
-          <t>19.747</t>
-        </is>
-      </c>
-      <c r="AO108" t="inlineStr">
-        <is>
-          <t>19.759375</t>
-        </is>
+      <c r="AN108" t="n">
+        <v>19.747</v>
+      </c>
+      <c r="AO108" t="n">
+        <v>19.759375</v>
       </c>
       <c r="AP108" t="inlineStr">
         <is>
@@ -42420,15 +41992,11 @@
           <t>19.775</t>
         </is>
       </c>
-      <c r="AN109" t="inlineStr">
-        <is>
-          <t>19.745</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>19.759375</t>
-        </is>
+      <c r="AN109" t="n">
+        <v>19.745</v>
+      </c>
+      <c r="AO109" t="n">
+        <v>19.759375</v>
       </c>
       <c r="AP109" t="inlineStr">
         <is>
@@ -42807,15 +42375,11 @@
           <t>19.775</t>
         </is>
       </c>
-      <c r="AN110" t="inlineStr">
-        <is>
-          <t>19.744</t>
-        </is>
-      </c>
-      <c r="AO110" t="inlineStr">
-        <is>
-          <t>19.76</t>
-        </is>
+      <c r="AN110" t="n">
+        <v>19.744</v>
+      </c>
+      <c r="AO110" t="n">
+        <v>19.76</v>
       </c>
       <c r="AP110" t="inlineStr">
         <is>
@@ -43194,15 +42758,11 @@
           <t>19.775</t>
         </is>
       </c>
-      <c r="AN111" t="inlineStr">
-        <is>
-          <t>19.745</t>
-        </is>
-      </c>
-      <c r="AO111" t="inlineStr">
-        <is>
-          <t>19.75875</t>
-        </is>
+      <c r="AN111" t="n">
+        <v>19.745</v>
+      </c>
+      <c r="AO111" t="n">
+        <v>19.75875</v>
       </c>
       <c r="AP111" t="inlineStr">
         <is>
@@ -43581,15 +43141,11 @@
           <t>35.975</t>
         </is>
       </c>
-      <c r="AN112" t="inlineStr">
-        <is>
-          <t>36.251</t>
-        </is>
-      </c>
-      <c r="AO112" t="inlineStr">
-        <is>
-          <t>36.3425</t>
-        </is>
+      <c r="AN112" t="n">
+        <v>36.251</v>
+      </c>
+      <c r="AO112" t="n">
+        <v>36.3425</v>
       </c>
       <c r="AP112" t="inlineStr">
         <is>
@@ -43968,15 +43524,11 @@
           <t>35.9825</t>
         </is>
       </c>
-      <c r="AN113" t="inlineStr">
-        <is>
-          <t>36.289</t>
-        </is>
-      </c>
-      <c r="AO113" t="inlineStr">
-        <is>
-          <t>36.343125</t>
-        </is>
+      <c r="AN113" t="n">
+        <v>36.289</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>36.343125</v>
       </c>
       <c r="AP113" t="inlineStr">
         <is>
@@ -44355,15 +43907,11 @@
           <t>36.0075</t>
         </is>
       </c>
-      <c r="AN114" t="inlineStr">
-        <is>
-          <t>36.332</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>36.345625</t>
-        </is>
+      <c r="AN114" t="n">
+        <v>36.332</v>
+      </c>
+      <c r="AO114" t="n">
+        <v>36.345625</v>
       </c>
       <c r="AP114" t="inlineStr">
         <is>
@@ -44742,15 +44290,11 @@
           <t>36.035</t>
         </is>
       </c>
-      <c r="AN115" t="inlineStr">
-        <is>
-          <t>36.36600000000001</t>
-        </is>
-      </c>
-      <c r="AO115" t="inlineStr">
-        <is>
-          <t>36.351875</t>
-        </is>
+      <c r="AN115" t="n">
+        <v>36.36600000000001</v>
+      </c>
+      <c r="AO115" t="n">
+        <v>36.351875</v>
       </c>
       <c r="AP115" t="inlineStr">
         <is>
@@ -45129,15 +44673,11 @@
           <t>36.065</t>
         </is>
       </c>
-      <c r="AN116" t="inlineStr">
-        <is>
-          <t>36.384</t>
-        </is>
-      </c>
-      <c r="AO116" t="inlineStr">
-        <is>
-          <t>36.353125</t>
-        </is>
+      <c r="AN116" t="n">
+        <v>36.384</v>
+      </c>
+      <c r="AO116" t="n">
+        <v>36.353125</v>
       </c>
       <c r="AP116" t="inlineStr">
         <is>
@@ -45516,15 +45056,11 @@
           <t>36.1</t>
         </is>
       </c>
-      <c r="AN117" t="inlineStr">
-        <is>
-          <t>36.402</t>
-        </is>
-      </c>
-      <c r="AO117" t="inlineStr">
-        <is>
-          <t>36.358125</t>
-        </is>
+      <c r="AN117" t="n">
+        <v>36.402</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>36.358125</v>
       </c>
       <c r="AP117" t="inlineStr">
         <is>
@@ -45903,15 +45439,11 @@
           <t>36.14</t>
         </is>
       </c>
-      <c r="AN118" t="inlineStr">
-        <is>
-          <t>36.426</t>
-        </is>
-      </c>
-      <c r="AO118" t="inlineStr">
-        <is>
-          <t>36.363125</t>
-        </is>
+      <c r="AN118" t="n">
+        <v>36.426</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>36.363125</v>
       </c>
       <c r="AP118" t="inlineStr">
         <is>
@@ -46290,15 +45822,11 @@
           <t>36.17</t>
         </is>
       </c>
-      <c r="AN119" t="inlineStr">
-        <is>
-          <t>36.46299999999999</t>
-        </is>
-      </c>
-      <c r="AO119" t="inlineStr">
-        <is>
-          <t>36.375</t>
-        </is>
+      <c r="AN119" t="n">
+        <v>36.46299999999999</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>36.375</v>
       </c>
       <c r="AP119" t="inlineStr">
         <is>
@@ -46677,15 +46205,11 @@
           <t>36.21</t>
         </is>
       </c>
-      <c r="AN120" t="inlineStr">
-        <is>
-          <t>36.501</t>
-        </is>
-      </c>
-      <c r="AO120" t="inlineStr">
-        <is>
-          <t>36.386875</t>
-        </is>
+      <c r="AN120" t="n">
+        <v>36.501</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>36.386875</v>
       </c>
       <c r="AP120" t="inlineStr">
         <is>
@@ -47064,15 +46588,11 @@
           <t>36.2375</t>
         </is>
       </c>
-      <c r="AN121" t="inlineStr">
-        <is>
-          <t>36.54</t>
-        </is>
-      </c>
-      <c r="AO121" t="inlineStr">
-        <is>
-          <t>36.396875</t>
-        </is>
+      <c r="AN121" t="n">
+        <v>36.54</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>36.396875</v>
       </c>
       <c r="AP121" t="inlineStr">
         <is>
@@ -47451,15 +46971,11 @@
           <t>64.66999999999999</t>
         </is>
       </c>
-      <c r="AN122" t="inlineStr">
-        <is>
-          <t>64.84200000000001</t>
-        </is>
-      </c>
-      <c r="AO122" t="inlineStr">
-        <is>
-          <t>65.33874999999999</t>
-        </is>
+      <c r="AN122" t="n">
+        <v>64.84200000000001</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>65.33874999999999</v>
       </c>
       <c r="AP122" t="inlineStr">
         <is>
@@ -47838,15 +47354,11 @@
           <t>64.72</t>
         </is>
       </c>
-      <c r="AN123" t="inlineStr">
-        <is>
-          <t>64.87799999999999</t>
-        </is>
-      </c>
-      <c r="AO123" t="inlineStr">
-        <is>
-          <t>65.375</t>
-        </is>
+      <c r="AN123" t="n">
+        <v>64.87799999999999</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>65.375</v>
       </c>
       <c r="AP123" t="inlineStr">
         <is>
@@ -48225,15 +47737,11 @@
           <t>64.73</t>
         </is>
       </c>
-      <c r="AN124" t="inlineStr">
-        <is>
-          <t>64.91</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>65.40625</t>
-        </is>
+      <c r="AN124" t="n">
+        <v>64.91</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>65.40625</v>
       </c>
       <c r="AP124" t="inlineStr">
         <is>
@@ -48612,15 +48120,11 @@
           <t>64.715</t>
         </is>
       </c>
-      <c r="AN125" t="inlineStr">
-        <is>
-          <t>64.936</t>
-        </is>
-      </c>
-      <c r="AO125" t="inlineStr">
-        <is>
-          <t>65.42875000000001</t>
-        </is>
+      <c r="AN125" t="n">
+        <v>64.93600000000001</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>65.42875000000001</v>
       </c>
       <c r="AP125" t="inlineStr">
         <is>
@@ -48999,15 +48503,11 @@
           <t>64.67999999999999</t>
         </is>
       </c>
-      <c r="AN126" t="inlineStr">
-        <is>
-          <t>64.964</t>
-        </is>
-      </c>
-      <c r="AO126" t="inlineStr">
-        <is>
-          <t>65.45124999999999</t>
-        </is>
+      <c r="AN126" t="n">
+        <v>64.964</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>65.45124999999999</v>
       </c>
       <c r="AP126" t="inlineStr">
         <is>
@@ -49386,15 +48886,11 @@
           <t>64.65</t>
         </is>
       </c>
-      <c r="AN127" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="AO127" t="inlineStr">
-        <is>
-          <t>65.475</t>
-        </is>
+      <c r="AN127" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>65.47499999999999</v>
       </c>
       <c r="AP127" t="inlineStr">
         <is>
@@ -49773,15 +49269,11 @@
           <t>64.63</t>
         </is>
       </c>
-      <c r="AN128" t="inlineStr">
-        <is>
-          <t>65.036</t>
-        </is>
-      </c>
-      <c r="AO128" t="inlineStr">
-        <is>
-          <t>65.49749999999999</t>
-        </is>
+      <c r="AN128" t="n">
+        <v>65.036</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>65.49749999999999</v>
       </c>
       <c r="AP128" t="inlineStr">
         <is>
@@ -50160,15 +49652,11 @@
           <t>64.635</t>
         </is>
       </c>
-      <c r="AN129" t="inlineStr">
-        <is>
-          <t>65.066</t>
-        </is>
-      </c>
-      <c r="AO129" t="inlineStr">
-        <is>
-          <t>65.52250000000001</t>
-        </is>
+      <c r="AN129" t="n">
+        <v>65.066</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>65.52250000000001</v>
       </c>
       <c r="AP129" t="inlineStr">
         <is>
@@ -50547,15 +50035,11 @@
           <t>64.66</t>
         </is>
       </c>
-      <c r="AN130" t="inlineStr">
-        <is>
-          <t>65.10600000000001</t>
-        </is>
-      </c>
-      <c r="AO130" t="inlineStr">
-        <is>
-          <t>65.5475</t>
-        </is>
+      <c r="AN130" t="n">
+        <v>65.10600000000001</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>65.5475</v>
       </c>
       <c r="AP130" t="inlineStr">
         <is>
@@ -50934,15 +50418,11 @@
           <t>64.68</t>
         </is>
       </c>
-      <c r="AN131" t="inlineStr">
-        <is>
-          <t>65.142</t>
-        </is>
-      </c>
-      <c r="AO131" t="inlineStr">
-        <is>
-          <t>65.5725</t>
-        </is>
+      <c r="AN131" t="n">
+        <v>65.142</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>65.57250000000001</v>
       </c>
       <c r="AP131" t="inlineStr">
         <is>
@@ -51321,15 +50801,11 @@
           <t>7.342000000000001</t>
         </is>
       </c>
-      <c r="AN132" t="inlineStr">
-        <is>
-          <t>7.3284</t>
-        </is>
-      </c>
-      <c r="AO132" t="inlineStr">
-        <is>
-          <t>7.259625</t>
-        </is>
+      <c r="AN132" t="n">
+        <v>7.3284</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>7.259625</v>
       </c>
       <c r="AP132" t="inlineStr">
         <is>
@@ -51708,15 +51184,11 @@
           <t>7.331</t>
         </is>
       </c>
-      <c r="AN133" t="inlineStr">
-        <is>
-          <t>7.3262</t>
-        </is>
-      </c>
-      <c r="AO133" t="inlineStr">
-        <is>
-          <t>7.249875</t>
-        </is>
+      <c r="AN133" t="n">
+        <v>7.3262</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>7.249875</v>
       </c>
       <c r="AP133" t="inlineStr">
         <is>
@@ -52095,15 +51567,11 @@
           <t>7.3125</t>
         </is>
       </c>
-      <c r="AN134" t="inlineStr">
-        <is>
-          <t>7.3186</t>
-        </is>
-      </c>
-      <c r="AO134" t="inlineStr">
-        <is>
-          <t>7.239375</t>
-        </is>
+      <c r="AN134" t="n">
+        <v>7.3186</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>7.239375</v>
       </c>
       <c r="AP134" t="inlineStr">
         <is>
@@ -52482,15 +51950,11 @@
           <t>7.297</t>
         </is>
       </c>
-      <c r="AN135" t="inlineStr">
-        <is>
-          <t>7.3094</t>
-        </is>
-      </c>
-      <c r="AO135" t="inlineStr">
-        <is>
-          <t>7.229374999999999</t>
-        </is>
+      <c r="AN135" t="n">
+        <v>7.3094</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>7.229374999999999</v>
       </c>
       <c r="AP135" t="inlineStr">
         <is>
@@ -52869,15 +52333,11 @@
           <t>7.287000000000001</t>
         </is>
       </c>
-      <c r="AN136" t="inlineStr">
-        <is>
-          <t>7.306</t>
-        </is>
-      </c>
-      <c r="AO136" t="inlineStr">
-        <is>
-          <t>7.220999999999999</t>
-        </is>
+      <c r="AN136" t="n">
+        <v>7.306</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>7.220999999999999</v>
       </c>
       <c r="AP136" t="inlineStr">
         <is>
@@ -53256,15 +52716,11 @@
           <t>7.2765</t>
         </is>
       </c>
-      <c r="AN137" t="inlineStr">
-        <is>
-          <t>7.3028</t>
-        </is>
-      </c>
-      <c r="AO137" t="inlineStr">
-        <is>
-          <t>7.211374999999999</t>
-        </is>
+      <c r="AN137" t="n">
+        <v>7.3028</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>7.211374999999999</v>
       </c>
       <c r="AP137" t="inlineStr">
         <is>
@@ -53643,15 +53099,11 @@
           <t>7.277000000000001</t>
         </is>
       </c>
-      <c r="AN138" t="inlineStr">
-        <is>
-          <t>7.3</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>7.201625</t>
-        </is>
+      <c r="AN138" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>7.201625</v>
       </c>
       <c r="AP138" t="inlineStr">
         <is>
@@ -54030,15 +53482,11 @@
           <t>7.282000000000001</t>
         </is>
       </c>
-      <c r="AN139" t="inlineStr">
-        <is>
-          <t>7.2962</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>7.193249999999999</t>
-        </is>
+      <c r="AN139" t="n">
+        <v>7.2962</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>7.193249999999999</v>
       </c>
       <c r="AP139" t="inlineStr">
         <is>
@@ -54417,15 +53865,11 @@
           <t>7.282000000000001</t>
         </is>
       </c>
-      <c r="AN140" t="inlineStr">
-        <is>
-          <t>7.2926</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>7.184</t>
-        </is>
+      <c r="AN140" t="n">
+        <v>7.2926</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>7.184</v>
       </c>
       <c r="AP140" t="inlineStr">
         <is>
@@ -54804,15 +54248,11 @@
           <t>7.282999999999999</t>
         </is>
       </c>
-      <c r="AN141" t="inlineStr">
-        <is>
-          <t>7.289400000000001</t>
-        </is>
-      </c>
-      <c r="AO141" t="inlineStr">
-        <is>
-          <t>7.174249999999999</t>
-        </is>
+      <c r="AN141" t="n">
+        <v>7.289400000000001</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>7.174249999999999</v>
       </c>
       <c r="AP141" t="inlineStr">
         <is>
@@ -55191,15 +54631,11 @@
           <t>10.3975</t>
         </is>
       </c>
-      <c r="AN142" t="inlineStr">
-        <is>
-          <t>10.277</t>
-        </is>
-      </c>
-      <c r="AO142" t="inlineStr">
-        <is>
-          <t>10.013625</t>
-        </is>
+      <c r="AN142" t="n">
+        <v>10.277</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>10.013625</v>
       </c>
       <c r="AP142" t="inlineStr">
         <is>
@@ -55578,15 +55014,11 @@
           <t>10.4125</t>
         </is>
       </c>
-      <c r="AN143" t="inlineStr">
-        <is>
-          <t>10.295</t>
-        </is>
-      </c>
-      <c r="AO143" t="inlineStr">
-        <is>
-          <t>9.98725</t>
-        </is>
+      <c r="AN143" t="n">
+        <v>10.295</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>9.98725</v>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
@@ -55965,15 +55397,11 @@
           <t>10.4275</t>
         </is>
       </c>
-      <c r="AN144" t="inlineStr">
-        <is>
-          <t>10.293</t>
-        </is>
-      </c>
-      <c r="AO144" t="inlineStr">
-        <is>
-          <t>9.957875</t>
-        </is>
+      <c r="AN144" t="n">
+        <v>10.293</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>9.957875</v>
       </c>
       <c r="AP144" t="inlineStr">
         <is>
@@ -56352,15 +55780,11 @@
           <t>10.445</t>
         </is>
       </c>
-      <c r="AN145" t="inlineStr">
-        <is>
-          <t>10.291</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>9.929625</t>
-        </is>
+      <c r="AN145" t="n">
+        <v>10.291</v>
+      </c>
+      <c r="AO145" t="n">
+        <v>9.929625</v>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
@@ -56739,15 +56163,11 @@
           <t>10.435</t>
         </is>
       </c>
-      <c r="AN146" t="inlineStr">
-        <is>
-          <t>10.287</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>9.898625</t>
-        </is>
+      <c r="AN146" t="n">
+        <v>10.287</v>
+      </c>
+      <c r="AO146" t="n">
+        <v>9.898624999999999</v>
       </c>
       <c r="AP146" t="inlineStr">
         <is>
@@ -57126,15 +56546,11 @@
           <t>10.43</t>
         </is>
       </c>
-      <c r="AN147" t="inlineStr">
-        <is>
-          <t>10.276</t>
-        </is>
-      </c>
-      <c r="AO147" t="inlineStr">
-        <is>
-          <t>9.862375</t>
-        </is>
+      <c r="AN147" t="n">
+        <v>10.276</v>
+      </c>
+      <c r="AO147" t="n">
+        <v>9.862375</v>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
@@ -57513,15 +56929,11 @@
           <t>10.4025</t>
         </is>
       </c>
-      <c r="AN148" t="inlineStr">
-        <is>
-          <t>10.2566</t>
-        </is>
-      </c>
-      <c r="AO148" t="inlineStr">
-        <is>
-          <t>9.82425</t>
-        </is>
+      <c r="AN148" t="n">
+        <v>10.2566</v>
+      </c>
+      <c r="AO148" t="n">
+        <v>9.824249999999999</v>
       </c>
       <c r="AP148" t="inlineStr">
         <is>
@@ -57900,15 +57312,11 @@
           <t>10.376</t>
         </is>
       </c>
-      <c r="AN149" t="inlineStr">
-        <is>
-          <t>10.2398</t>
-        </is>
-      </c>
-      <c r="AO149" t="inlineStr">
-        <is>
-          <t>9.790875000000002</t>
-        </is>
+      <c r="AN149" t="n">
+        <v>10.2398</v>
+      </c>
+      <c r="AO149" t="n">
+        <v>9.790875000000002</v>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
@@ -58287,15 +57695,11 @@
           <t>10.361</t>
         </is>
       </c>
-      <c r="AN150" t="inlineStr">
-        <is>
-          <t>10.2296</t>
-        </is>
-      </c>
-      <c r="AO150" t="inlineStr">
-        <is>
-          <t>9.75975</t>
-        </is>
+      <c r="AN150" t="n">
+        <v>10.2296</v>
+      </c>
+      <c r="AO150" t="n">
+        <v>9.75975</v>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
@@ -58674,15 +58078,11 @@
           <t>10.3265</t>
         </is>
       </c>
-      <c r="AN151" t="inlineStr">
-        <is>
-          <t>10.2186</t>
-        </is>
-      </c>
-      <c r="AO151" t="inlineStr">
-        <is>
-          <t>9.72825</t>
-        </is>
+      <c r="AN151" t="n">
+        <v>10.2186</v>
+      </c>
+      <c r="AO151" t="n">
+        <v>9.728249999999999</v>
       </c>
       <c r="AP151" t="inlineStr">
         <is>
@@ -59061,15 +58461,11 @@
           <t>10.1615</t>
         </is>
       </c>
-      <c r="AN152" t="inlineStr">
-        <is>
-          <t>9.907</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>9.874374999999999</t>
-        </is>
+      <c r="AN152" t="n">
+        <v>9.907</v>
+      </c>
+      <c r="AO152" t="n">
+        <v>9.874375000000001</v>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
@@ -59448,15 +58844,11 @@
           <t>10.1235</t>
         </is>
       </c>
-      <c r="AN153" t="inlineStr">
-        <is>
-          <t>9.907</t>
-        </is>
-      </c>
-      <c r="AO153" t="inlineStr">
-        <is>
-          <t>9.8625</t>
-        </is>
+      <c r="AN153" t="n">
+        <v>9.907</v>
+      </c>
+      <c r="AO153" t="n">
+        <v>9.862500000000001</v>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
@@ -59835,15 +59227,11 @@
           <t>10.076</t>
         </is>
       </c>
-      <c r="AN154" t="inlineStr">
-        <is>
-          <t>9.9</t>
-        </is>
-      </c>
-      <c r="AO154" t="inlineStr">
-        <is>
-          <t>9.8495</t>
-        </is>
+      <c r="AN154" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="AO154" t="n">
+        <v>9.849500000000001</v>
       </c>
       <c r="AP154" t="inlineStr">
         <is>
@@ -60222,15 +59610,11 @@
           <t>10.0305</t>
         </is>
       </c>
-      <c r="AN155" t="inlineStr">
-        <is>
-          <t>9.891</t>
-        </is>
-      </c>
-      <c r="AO155" t="inlineStr">
-        <is>
-          <t>9.837</t>
-        </is>
+      <c r="AN155" t="n">
+        <v>9.891</v>
+      </c>
+      <c r="AO155" t="n">
+        <v>9.837</v>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
@@ -60609,15 +59993,11 @@
           <t>9.967500000000001</t>
         </is>
       </c>
-      <c r="AN156" t="inlineStr">
-        <is>
-          <t>9.88</t>
-        </is>
-      </c>
-      <c r="AO156" t="inlineStr">
-        <is>
-          <t>9.8215</t>
-        </is>
+      <c r="AN156" t="n">
+        <v>9.880000000000001</v>
+      </c>
+      <c r="AO156" t="n">
+        <v>9.8215</v>
       </c>
       <c r="AP156" t="inlineStr">
         <is>
@@ -60996,15 +60376,11 @@
           <t>9.903</t>
         </is>
       </c>
-      <c r="AN157" t="inlineStr">
-        <is>
-          <t>9.865</t>
-        </is>
-      </c>
-      <c r="AO157" t="inlineStr">
-        <is>
-          <t>9.803125</t>
-        </is>
+      <c r="AN157" t="n">
+        <v>9.865</v>
+      </c>
+      <c r="AO157" t="n">
+        <v>9.803125</v>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
@@ -61383,15 +60759,11 @@
           <t>9.825500000000002</t>
         </is>
       </c>
-      <c r="AN158" t="inlineStr">
-        <is>
-          <t>9.8398</t>
-        </is>
-      </c>
-      <c r="AO158" t="inlineStr">
-        <is>
-          <t>9.78275</t>
-        </is>
+      <c r="AN158" t="n">
+        <v>9.8398</v>
+      </c>
+      <c r="AO158" t="n">
+        <v>9.78275</v>
       </c>
       <c r="AP158" t="inlineStr">
         <is>
@@ -61770,15 +61142,11 @@
           <t>9.7585</t>
         </is>
       </c>
-      <c r="AN159" t="inlineStr">
-        <is>
-          <t>9.814400000000001</t>
-        </is>
-      </c>
-      <c r="AO159" t="inlineStr">
-        <is>
-          <t>9.767125</t>
-        </is>
+      <c r="AN159" t="n">
+        <v>9.814399999999999</v>
+      </c>
+      <c r="AO159" t="n">
+        <v>9.767125</v>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
@@ -62157,15 +61525,11 @@
           <t>9.711</t>
         </is>
       </c>
-      <c r="AN160" t="inlineStr">
-        <is>
-          <t>9.801</t>
-        </is>
-      </c>
-      <c r="AO160" t="inlineStr">
-        <is>
-          <t>9.757</t>
-        </is>
+      <c r="AN160" t="n">
+        <v>9.801</v>
+      </c>
+      <c r="AO160" t="n">
+        <v>9.757</v>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
@@ -62544,15 +61908,11 @@
           <t>9.662</t>
         </is>
       </c>
-      <c r="AN161" t="inlineStr">
-        <is>
-          <t>9.7876</t>
-        </is>
-      </c>
-      <c r="AO161" t="inlineStr">
-        <is>
-          <t>9.744375</t>
-        </is>
+      <c r="AN161" t="n">
+        <v>9.787599999999999</v>
+      </c>
+      <c r="AO161" t="n">
+        <v>9.744375</v>
       </c>
       <c r="AP161" t="inlineStr">
         <is>
@@ -62931,15 +62291,11 @@
           <t>8.7205</t>
         </is>
       </c>
-      <c r="AN162" t="inlineStr">
-        <is>
-          <t>8.904</t>
-        </is>
-      </c>
-      <c r="AO162" t="inlineStr">
-        <is>
-          <t>8.868500000000001</t>
-        </is>
+      <c r="AN162" t="n">
+        <v>8.904</v>
+      </c>
+      <c r="AO162" t="n">
+        <v>8.868500000000001</v>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
@@ -63318,15 +62674,11 @@
           <t>8.732000000000001</t>
         </is>
       </c>
-      <c r="AN163" t="inlineStr">
-        <is>
-          <t>8.9284</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>8.86175</t>
-        </is>
+      <c r="AN163" t="n">
+        <v>8.9284</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>8.861750000000001</v>
       </c>
       <c r="AP163" t="inlineStr">
         <is>
@@ -63705,15 +63057,11 @@
           <t>8.732499999999998</t>
         </is>
       </c>
-      <c r="AN164" t="inlineStr">
-        <is>
-          <t>8.9466</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>8.851875000000001</t>
-        </is>
+      <c r="AN164" t="n">
+        <v>8.9466</v>
+      </c>
+      <c r="AO164" t="n">
+        <v>8.851875000000001</v>
       </c>
       <c r="AP164" t="inlineStr">
         <is>
@@ -64092,15 +63440,11 @@
           <t>8.736</t>
         </is>
       </c>
-      <c r="AN165" t="inlineStr">
-        <is>
-          <t>8.9608</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>8.842250000000002</t>
-        </is>
+      <c r="AN165" t="n">
+        <v>8.960800000000001</v>
+      </c>
+      <c r="AO165" t="n">
+        <v>8.842250000000002</v>
       </c>
       <c r="AP165" t="inlineStr">
         <is>
@@ -64479,15 +63823,11 @@
           <t>8.7225</t>
         </is>
       </c>
-      <c r="AN166" t="inlineStr">
-        <is>
-          <t>8.9726</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>8.828750000000001</t>
-        </is>
+      <c r="AN166" t="n">
+        <v>8.9726</v>
+      </c>
+      <c r="AO166" t="n">
+        <v>8.828750000000001</v>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
@@ -64866,15 +64206,11 @@
           <t>8.704500000000001</t>
         </is>
       </c>
-      <c r="AN167" t="inlineStr">
-        <is>
-          <t>8.982000000000001</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>8.81225</t>
-        </is>
+      <c r="AN167" t="n">
+        <v>8.982000000000001</v>
+      </c>
+      <c r="AO167" t="n">
+        <v>8.812250000000001</v>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
@@ -65253,15 +64589,11 @@
           <t>8.6845</t>
         </is>
       </c>
-      <c r="AN168" t="inlineStr">
-        <is>
-          <t>8.9884</t>
-        </is>
-      </c>
-      <c r="AO168" t="inlineStr">
-        <is>
-          <t>8.795625</t>
-        </is>
+      <c r="AN168" t="n">
+        <v>8.9884</v>
+      </c>
+      <c r="AO168" t="n">
+        <v>8.795624999999999</v>
       </c>
       <c r="AP168" t="inlineStr">
         <is>
@@ -65640,15 +64972,11 @@
           <t>8.672</t>
         </is>
       </c>
-      <c r="AN169" t="inlineStr">
-        <is>
-          <t>8.991800000000001</t>
-        </is>
-      </c>
-      <c r="AO169" t="inlineStr">
-        <is>
-          <t>8.782625</t>
-        </is>
+      <c r="AN169" t="n">
+        <v>8.991800000000001</v>
+      </c>
+      <c r="AO169" t="n">
+        <v>8.782624999999999</v>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
@@ -66027,15 +65355,11 @@
           <t>8.6715</t>
         </is>
       </c>
-      <c r="AN170" t="inlineStr">
-        <is>
-          <t>8.9992</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>8.7715</t>
-        </is>
+      <c r="AN170" t="n">
+        <v>8.9992</v>
+      </c>
+      <c r="AO170" t="n">
+        <v>8.7715</v>
       </c>
       <c r="AP170" t="inlineStr">
         <is>
@@ -66414,15 +65738,11 @@
           <t>8.666</t>
         </is>
       </c>
-      <c r="AN171" t="inlineStr">
-        <is>
-          <t>9.0088</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>8.759625000000002</t>
-        </is>
+      <c r="AN171" t="n">
+        <v>9.008800000000001</v>
+      </c>
+      <c r="AO171" t="n">
+        <v>8.759625000000002</v>
       </c>
       <c r="AP171" t="inlineStr">
         <is>
@@ -66801,15 +66121,11 @@
           <t>11.115</t>
         </is>
       </c>
-      <c r="AN172" t="inlineStr">
-        <is>
-          <t>11.209</t>
-        </is>
-      </c>
-      <c r="AO172" t="inlineStr">
-        <is>
-          <t>11.17925</t>
-        </is>
+      <c r="AN172" t="n">
+        <v>11.209</v>
+      </c>
+      <c r="AO172" t="n">
+        <v>11.17925</v>
       </c>
       <c r="AP172" t="inlineStr">
         <is>
@@ -67188,15 +66504,11 @@
           <t>11.1025</t>
         </is>
       </c>
-      <c r="AN173" t="inlineStr">
-        <is>
-          <t>11.233</t>
-        </is>
-      </c>
-      <c r="AO173" t="inlineStr">
-        <is>
-          <t>11.168625</t>
-        </is>
+      <c r="AN173" t="n">
+        <v>11.233</v>
+      </c>
+      <c r="AO173" t="n">
+        <v>11.168625</v>
       </c>
       <c r="AP173" t="inlineStr">
         <is>
@@ -67575,15 +66887,11 @@
           <t>11.0825</t>
         </is>
       </c>
-      <c r="AN174" t="inlineStr">
-        <is>
-          <t>11.246</t>
-        </is>
-      </c>
-      <c r="AO174" t="inlineStr">
-        <is>
-          <t>11.158</t>
-        </is>
+      <c r="AN174" t="n">
+        <v>11.246</v>
+      </c>
+      <c r="AO174" t="n">
+        <v>11.158</v>
       </c>
       <c r="AP174" t="inlineStr">
         <is>
@@ -67962,15 +67270,11 @@
           <t>11.065</t>
         </is>
       </c>
-      <c r="AN175" t="inlineStr">
-        <is>
-          <t>11.256</t>
-        </is>
-      </c>
-      <c r="AO175" t="inlineStr">
-        <is>
-          <t>11.148</t>
-        </is>
+      <c r="AN175" t="n">
+        <v>11.256</v>
+      </c>
+      <c r="AO175" t="n">
+        <v>11.148</v>
       </c>
       <c r="AP175" t="inlineStr">
         <is>
@@ -68349,15 +67653,11 @@
           <t>11.04</t>
         </is>
       </c>
-      <c r="AN176" t="inlineStr">
-        <is>
-          <t>11.267</t>
-        </is>
-      </c>
-      <c r="AO176" t="inlineStr">
-        <is>
-          <t>11.136125</t>
-        </is>
+      <c r="AN176" t="n">
+        <v>11.267</v>
+      </c>
+      <c r="AO176" t="n">
+        <v>11.136125</v>
       </c>
       <c r="AP176" t="inlineStr">
         <is>
@@ -68736,15 +68036,11 @@
           <t>11.0075</t>
         </is>
       </c>
-      <c r="AN177" t="inlineStr">
-        <is>
-          <t>11.272</t>
-        </is>
-      </c>
-      <c r="AO177" t="inlineStr">
-        <is>
-          <t>11.121125</t>
-        </is>
+      <c r="AN177" t="n">
+        <v>11.272</v>
+      </c>
+      <c r="AO177" t="n">
+        <v>11.121125</v>
       </c>
       <c r="AP177" t="inlineStr">
         <is>
@@ -69123,15 +68419,11 @@
           <t>10.9725</t>
         </is>
       </c>
-      <c r="AN178" t="inlineStr">
-        <is>
-          <t>11.268</t>
-        </is>
-      </c>
-      <c r="AO178" t="inlineStr">
-        <is>
-          <t>11.103</t>
-        </is>
+      <c r="AN178" t="n">
+        <v>11.268</v>
+      </c>
+      <c r="AO178" t="n">
+        <v>11.103</v>
       </c>
       <c r="AP178" t="inlineStr">
         <is>
@@ -69510,15 +68802,11 @@
           <t>10.95</t>
         </is>
       </c>
-      <c r="AN179" t="inlineStr">
-        <is>
-          <t>11.268</t>
-        </is>
-      </c>
-      <c r="AO179" t="inlineStr">
-        <is>
-          <t>11.0905</t>
-        </is>
+      <c r="AN179" t="n">
+        <v>11.268</v>
+      </c>
+      <c r="AO179" t="n">
+        <v>11.0905</v>
       </c>
       <c r="AP179" t="inlineStr">
         <is>
@@ -69897,15 +69185,11 @@
           <t>10.9425</t>
         </is>
       </c>
-      <c r="AN180" t="inlineStr">
-        <is>
-          <t>11.272</t>
-        </is>
-      </c>
-      <c r="AO180" t="inlineStr">
-        <is>
-          <t>11.08175</t>
-        </is>
+      <c r="AN180" t="n">
+        <v>11.272</v>
+      </c>
+      <c r="AO180" t="n">
+        <v>11.08175</v>
       </c>
       <c r="AP180" t="inlineStr">
         <is>
@@ -70284,15 +69568,11 @@
           <t>10.925</t>
         </is>
       </c>
-      <c r="AN181" t="inlineStr">
-        <is>
-          <t>11.274</t>
-        </is>
-      </c>
-      <c r="AO181" t="inlineStr">
-        <is>
-          <t>11.0705</t>
-        </is>
+      <c r="AN181" t="n">
+        <v>11.274</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>11.0705</v>
       </c>
       <c r="AP181" t="inlineStr">
         <is>
@@ -70671,15 +69951,11 @@
           <t>12.7375</t>
         </is>
       </c>
-      <c r="AN182" t="inlineStr">
-        <is>
-          <t>12.298</t>
-        </is>
-      </c>
-      <c r="AO182" t="inlineStr">
-        <is>
-          <t>12.171875</t>
-        </is>
+      <c r="AN182" t="n">
+        <v>12.298</v>
+      </c>
+      <c r="AO182" t="n">
+        <v>12.171875</v>
       </c>
       <c r="AP182" t="inlineStr">
         <is>
@@ -71058,15 +70334,11 @@
           <t>12.6975</t>
         </is>
       </c>
-      <c r="AN183" t="inlineStr">
-        <is>
-          <t>12.302</t>
-        </is>
-      </c>
-      <c r="AO183" t="inlineStr">
-        <is>
-          <t>12.15875</t>
-        </is>
+      <c r="AN183" t="n">
+        <v>12.302</v>
+      </c>
+      <c r="AO183" t="n">
+        <v>12.15875</v>
       </c>
       <c r="AP183" t="inlineStr">
         <is>
@@ -71445,15 +70717,11 @@
           <t>12.6425</t>
         </is>
       </c>
-      <c r="AN184" t="inlineStr">
-        <is>
-          <t>12.294</t>
-        </is>
-      </c>
-      <c r="AO184" t="inlineStr">
-        <is>
-          <t>12.144375</t>
-        </is>
+      <c r="AN184" t="n">
+        <v>12.294</v>
+      </c>
+      <c r="AO184" t="n">
+        <v>12.144375</v>
       </c>
       <c r="AP184" t="inlineStr">
         <is>
@@ -71832,15 +71100,11 @@
           <t>12.59</t>
         </is>
       </c>
-      <c r="AN185" t="inlineStr">
-        <is>
-          <t>12.28</t>
-        </is>
-      </c>
-      <c r="AO185" t="inlineStr">
-        <is>
-          <t>12.13</t>
-        </is>
+      <c r="AN185" t="n">
+        <v>12.28</v>
+      </c>
+      <c r="AO185" t="n">
+        <v>12.13</v>
       </c>
       <c r="AP185" t="inlineStr">
         <is>
@@ -72219,15 +71483,11 @@
           <t>12.515</t>
         </is>
       </c>
-      <c r="AN186" t="inlineStr">
-        <is>
-          <t>12.264</t>
-        </is>
-      </c>
-      <c r="AO186" t="inlineStr">
-        <is>
-          <t>12.110625</t>
-        </is>
+      <c r="AN186" t="n">
+        <v>12.264</v>
+      </c>
+      <c r="AO186" t="n">
+        <v>12.110625</v>
       </c>
       <c r="AP186" t="inlineStr">
         <is>
@@ -72606,15 +71866,11 @@
           <t>12.4225</t>
         </is>
       </c>
-      <c r="AN187" t="inlineStr">
-        <is>
-          <t>12.239</t>
-        </is>
-      </c>
-      <c r="AO187" t="inlineStr">
-        <is>
-          <t>12.085625</t>
-        </is>
+      <c r="AN187" t="n">
+        <v>12.239</v>
+      </c>
+      <c r="AO187" t="n">
+        <v>12.085625</v>
       </c>
       <c r="AP187" t="inlineStr">
         <is>
@@ -72993,15 +72249,11 @@
           <t>12.33</t>
         </is>
       </c>
-      <c r="AN188" t="inlineStr">
-        <is>
-          <t>12.201</t>
-        </is>
-      </c>
-      <c r="AO188" t="inlineStr">
-        <is>
-          <t>12.058125</t>
-        </is>
+      <c r="AN188" t="n">
+        <v>12.201</v>
+      </c>
+      <c r="AO188" t="n">
+        <v>12.058125</v>
       </c>
       <c r="AP188" t="inlineStr">
         <is>
@@ -73380,15 +72632,11 @@
           <t>12.265</t>
         </is>
       </c>
-      <c r="AN189" t="inlineStr">
-        <is>
-          <t>12.176</t>
-        </is>
-      </c>
-      <c r="AO189" t="inlineStr">
-        <is>
-          <t>12.040625</t>
-        </is>
+      <c r="AN189" t="n">
+        <v>12.176</v>
+      </c>
+      <c r="AO189" t="n">
+        <v>12.040625</v>
       </c>
       <c r="AP189" t="inlineStr">
         <is>
@@ -73767,15 +73015,11 @@
           <t>12.2025</t>
         </is>
       </c>
-      <c r="AN190" t="inlineStr">
-        <is>
-          <t>12.157</t>
-        </is>
-      </c>
-      <c r="AO190" t="inlineStr">
-        <is>
-          <t>12.025625</t>
-        </is>
+      <c r="AN190" t="n">
+        <v>12.157</v>
+      </c>
+      <c r="AO190" t="n">
+        <v>12.025625</v>
       </c>
       <c r="AP190" t="inlineStr">
         <is>
@@ -74154,15 +73398,11 @@
           <t>12.1325</t>
         </is>
       </c>
-      <c r="AN191" t="inlineStr">
-        <is>
-          <t>12.136</t>
-        </is>
-      </c>
-      <c r="AO191" t="inlineStr">
-        <is>
-          <t>12.00875</t>
-        </is>
+      <c r="AN191" t="n">
+        <v>12.136</v>
+      </c>
+      <c r="AO191" t="n">
+        <v>12.00875</v>
       </c>
       <c r="AP191" t="inlineStr">
         <is>
@@ -74541,15 +73781,11 @@
           <t>30.8075</t>
         </is>
       </c>
-      <c r="AN192" t="inlineStr">
-        <is>
-          <t>30.766</t>
-        </is>
-      </c>
-      <c r="AO192" t="inlineStr">
-        <is>
-          <t>31.776875</t>
-        </is>
+      <c r="AN192" t="n">
+        <v>30.766</v>
+      </c>
+      <c r="AO192" t="n">
+        <v>31.776875</v>
       </c>
       <c r="AP192" t="inlineStr">
         <is>
@@ -74928,15 +74164,11 @@
           <t>30.7675</t>
         </is>
       </c>
-      <c r="AN193" t="inlineStr">
-        <is>
-          <t>30.792</t>
-        </is>
-      </c>
-      <c r="AO193" t="inlineStr">
-        <is>
-          <t>31.86875</t>
-        </is>
+      <c r="AN193" t="n">
+        <v>30.792</v>
+      </c>
+      <c r="AO193" t="n">
+        <v>31.86875</v>
       </c>
       <c r="AP193" t="inlineStr">
         <is>
@@ -75315,15 +74547,11 @@
           <t>30.74</t>
         </is>
       </c>
-      <c r="AN194" t="inlineStr">
-        <is>
-          <t>30.833</t>
-        </is>
-      </c>
-      <c r="AO194" t="inlineStr">
-        <is>
-          <t>31.966875</t>
-        </is>
+      <c r="AN194" t="n">
+        <v>30.833</v>
+      </c>
+      <c r="AO194" t="n">
+        <v>31.966875</v>
       </c>
       <c r="AP194" t="inlineStr">
         <is>
@@ -75702,15 +74930,11 @@
           <t>30.7125</t>
         </is>
       </c>
-      <c r="AN195" t="inlineStr">
-        <is>
-          <t>30.849</t>
-        </is>
-      </c>
-      <c r="AO195" t="inlineStr">
-        <is>
-          <t>32.063125</t>
-        </is>
+      <c r="AN195" t="n">
+        <v>30.849</v>
+      </c>
+      <c r="AO195" t="n">
+        <v>32.063125</v>
       </c>
       <c r="AP195" t="inlineStr">
         <is>
@@ -76089,15 +75313,11 @@
           <t>30.675</t>
         </is>
       </c>
-      <c r="AN196" t="inlineStr">
-        <is>
-          <t>30.856</t>
-        </is>
-      </c>
-      <c r="AO196" t="inlineStr">
-        <is>
-          <t>32.15</t>
-        </is>
+      <c r="AN196" t="n">
+        <v>30.856</v>
+      </c>
+      <c r="AO196" t="n">
+        <v>32.15</v>
       </c>
       <c r="AP196" t="inlineStr">
         <is>
@@ -76476,15 +75696,11 @@
           <t>30.595</t>
         </is>
       </c>
-      <c r="AN197" t="inlineStr">
-        <is>
-          <t>30.843</t>
-        </is>
-      </c>
-      <c r="AO197" t="inlineStr">
-        <is>
-          <t>32.22625</t>
-        </is>
+      <c r="AN197" t="n">
+        <v>30.843</v>
+      </c>
+      <c r="AO197" t="n">
+        <v>32.22625</v>
       </c>
       <c r="AP197" t="inlineStr">
         <is>
@@ -76863,15 +76079,11 @@
           <t>30.5</t>
         </is>
       </c>
-      <c r="AN198" t="inlineStr">
-        <is>
-          <t>30.82100000000001</t>
-        </is>
-      </c>
-      <c r="AO198" t="inlineStr">
-        <is>
-          <t>32.296875</t>
-        </is>
+      <c r="AN198" t="n">
+        <v>30.82100000000001</v>
+      </c>
+      <c r="AO198" t="n">
+        <v>32.296875</v>
       </c>
       <c r="AP198" t="inlineStr">
         <is>
@@ -77250,15 +76462,11 @@
           <t>30.43</t>
         </is>
       </c>
-      <c r="AN199" t="inlineStr">
-        <is>
-          <t>30.82</t>
-        </is>
-      </c>
-      <c r="AO199" t="inlineStr">
-        <is>
-          <t>32.37</t>
-        </is>
+      <c r="AN199" t="n">
+        <v>30.82</v>
+      </c>
+      <c r="AO199" t="n">
+        <v>32.37</v>
       </c>
       <c r="AP199" t="inlineStr">
         <is>
@@ -77637,15 +76845,11 @@
           <t>30.37</t>
         </is>
       </c>
-      <c r="AN200" t="inlineStr">
-        <is>
-          <t>30.868</t>
-        </is>
-      </c>
-      <c r="AO200" t="inlineStr">
-        <is>
-          <t>32.450625</t>
-        </is>
+      <c r="AN200" t="n">
+        <v>30.868</v>
+      </c>
+      <c r="AO200" t="n">
+        <v>32.450625</v>
       </c>
       <c r="AP200" t="inlineStr">
         <is>
@@ -78024,15 +77228,11 @@
           <t>30.335</t>
         </is>
       </c>
-      <c r="AN201" t="inlineStr">
-        <is>
-          <t>30.936</t>
-        </is>
-      </c>
-      <c r="AO201" t="inlineStr">
-        <is>
-          <t>32.534375</t>
-        </is>
+      <c r="AN201" t="n">
+        <v>30.936</v>
+      </c>
+      <c r="AO201" t="n">
+        <v>32.534375</v>
       </c>
       <c r="AP201" t="inlineStr">
         <is>
@@ -78411,15 +77611,11 @@
           <t>11.34</t>
         </is>
       </c>
-      <c r="AN202" t="inlineStr">
-        <is>
-          <t>11.54</t>
-        </is>
-      </c>
-      <c r="AO202" t="inlineStr">
-        <is>
-          <t>11.349125</t>
-        </is>
+      <c r="AN202" t="n">
+        <v>11.54</v>
+      </c>
+      <c r="AO202" t="n">
+        <v>11.349125</v>
       </c>
       <c r="AP202" t="inlineStr">
         <is>
@@ -78798,15 +77994,11 @@
           <t>11.355</t>
         </is>
       </c>
-      <c r="AN203" t="inlineStr">
-        <is>
-          <t>11.556</t>
-        </is>
-      </c>
-      <c r="AO203" t="inlineStr">
-        <is>
-          <t>11.3345</t>
-        </is>
+      <c r="AN203" t="n">
+        <v>11.556</v>
+      </c>
+      <c r="AO203" t="n">
+        <v>11.3345</v>
       </c>
       <c r="AP203" t="inlineStr">
         <is>
@@ -79185,15 +78377,11 @@
           <t>11.3725</t>
         </is>
       </c>
-      <c r="AN204" t="inlineStr">
-        <is>
-          <t>11.565</t>
-        </is>
-      </c>
-      <c r="AO204" t="inlineStr">
-        <is>
-          <t>11.322</t>
-        </is>
+      <c r="AN204" t="n">
+        <v>11.565</v>
+      </c>
+      <c r="AO204" t="n">
+        <v>11.322</v>
       </c>
       <c r="AP204" t="inlineStr">
         <is>
@@ -79572,15 +78760,11 @@
           <t>11.395</t>
         </is>
       </c>
-      <c r="AN205" t="inlineStr">
-        <is>
-          <t>11.567</t>
-        </is>
-      </c>
-      <c r="AO205" t="inlineStr">
-        <is>
-          <t>11.30825</t>
-        </is>
+      <c r="AN205" t="n">
+        <v>11.567</v>
+      </c>
+      <c r="AO205" t="n">
+        <v>11.30825</v>
       </c>
       <c r="AP205" t="inlineStr">
         <is>
@@ -79959,15 +79143,11 @@
           <t>11.3975</t>
         </is>
       </c>
-      <c r="AN206" t="inlineStr">
-        <is>
-          <t>11.565</t>
-        </is>
-      </c>
-      <c r="AO206" t="inlineStr">
-        <is>
-          <t>11.2895</t>
-        </is>
+      <c r="AN206" t="n">
+        <v>11.565</v>
+      </c>
+      <c r="AO206" t="n">
+        <v>11.2895</v>
       </c>
       <c r="AP206" t="inlineStr">
         <is>
@@ -80346,15 +79526,11 @@
           <t>11.395</t>
         </is>
       </c>
-      <c r="AN207" t="inlineStr">
-        <is>
-          <t>11.561</t>
-        </is>
-      </c>
-      <c r="AO207" t="inlineStr">
-        <is>
-          <t>11.269</t>
-        </is>
+      <c r="AN207" t="n">
+        <v>11.561</v>
+      </c>
+      <c r="AO207" t="n">
+        <v>11.269</v>
       </c>
       <c r="AP207" t="inlineStr">
         <is>
@@ -80733,15 +79909,11 @@
           <t>11.385</t>
         </is>
       </c>
-      <c r="AN208" t="inlineStr">
-        <is>
-          <t>11.545</t>
-        </is>
-      </c>
-      <c r="AO208" t="inlineStr">
-        <is>
-          <t>11.245375</t>
-        </is>
+      <c r="AN208" t="n">
+        <v>11.545</v>
+      </c>
+      <c r="AO208" t="n">
+        <v>11.245375</v>
       </c>
       <c r="AP208" t="inlineStr">
         <is>
@@ -81120,15 +80292,11 @@
           <t>11.3975</t>
         </is>
       </c>
-      <c r="AN209" t="inlineStr">
-        <is>
-          <t>11.538</t>
-        </is>
-      </c>
-      <c r="AO209" t="inlineStr">
-        <is>
-          <t>11.22975</t>
-        </is>
+      <c r="AN209" t="n">
+        <v>11.538</v>
+      </c>
+      <c r="AO209" t="n">
+        <v>11.22975</v>
       </c>
       <c r="AP209" t="inlineStr">
         <is>
@@ -81507,15 +80675,11 @@
           <t>11.41</t>
         </is>
       </c>
-      <c r="AN210" t="inlineStr">
-        <is>
-          <t>11.535</t>
-        </is>
-      </c>
-      <c r="AO210" t="inlineStr">
-        <is>
-          <t>11.215375</t>
-        </is>
+      <c r="AN210" t="n">
+        <v>11.535</v>
+      </c>
+      <c r="AO210" t="n">
+        <v>11.215375</v>
       </c>
       <c r="AP210" t="inlineStr">
         <is>
@@ -81894,15 +81058,11 @@
           <t>11.41</t>
         </is>
       </c>
-      <c r="AN211" t="inlineStr">
-        <is>
-          <t>11.531</t>
-        </is>
-      </c>
-      <c r="AO211" t="inlineStr">
-        <is>
-          <t>11.199125</t>
-        </is>
+      <c r="AN211" t="n">
+        <v>11.531</v>
+      </c>
+      <c r="AO211" t="n">
+        <v>11.199125</v>
       </c>
       <c r="AP211" t="inlineStr">
         <is>
@@ -82281,15 +81441,11 @@
           <t>10.5525</t>
         </is>
       </c>
-      <c r="AN212" t="inlineStr">
-        <is>
-          <t>10.473</t>
-        </is>
-      </c>
-      <c r="AO212" t="inlineStr">
-        <is>
-          <t>10.4115</t>
-        </is>
+      <c r="AN212" t="n">
+        <v>10.473</v>
+      </c>
+      <c r="AO212" t="n">
+        <v>10.4115</v>
       </c>
       <c r="AP212" t="inlineStr">
         <is>
@@ -82668,15 +81824,11 @@
           <t>10.54</t>
         </is>
       </c>
-      <c r="AN213" t="inlineStr">
-        <is>
-          <t>10.491</t>
-        </is>
-      </c>
-      <c r="AO213" t="inlineStr">
-        <is>
-          <t>10.401125</t>
-        </is>
+      <c r="AN213" t="n">
+        <v>10.491</v>
+      </c>
+      <c r="AO213" t="n">
+        <v>10.401125</v>
       </c>
       <c r="AP213" t="inlineStr">
         <is>
@@ -83055,15 +82207,11 @@
           <t>10.515</t>
         </is>
       </c>
-      <c r="AN214" t="inlineStr">
-        <is>
-          <t>10.498</t>
-        </is>
-      </c>
-      <c r="AO214" t="inlineStr">
-        <is>
-          <t>10.388875</t>
-        </is>
+      <c r="AN214" t="n">
+        <v>10.498</v>
+      </c>
+      <c r="AO214" t="n">
+        <v>10.388875</v>
       </c>
       <c r="AP214" t="inlineStr">
         <is>
@@ -83442,15 +82590,11 @@
           <t>10.485</t>
         </is>
       </c>
-      <c r="AN215" t="inlineStr">
-        <is>
-          <t>10.497</t>
-        </is>
-      </c>
-      <c r="AO215" t="inlineStr">
-        <is>
-          <t>10.374125</t>
-        </is>
+      <c r="AN215" t="n">
+        <v>10.497</v>
+      </c>
+      <c r="AO215" t="n">
+        <v>10.374125</v>
       </c>
       <c r="AP215" t="inlineStr">
         <is>
@@ -83829,15 +82973,11 @@
           <t>10.4325</t>
         </is>
       </c>
-      <c r="AN216" t="inlineStr">
-        <is>
-          <t>10.495</t>
-        </is>
-      </c>
-      <c r="AO216" t="inlineStr">
-        <is>
-          <t>10.353625</t>
-        </is>
+      <c r="AN216" t="n">
+        <v>10.495</v>
+      </c>
+      <c r="AO216" t="n">
+        <v>10.353625</v>
       </c>
       <c r="AP216" t="inlineStr">
         <is>
@@ -84216,15 +83356,11 @@
           <t>10.3825</t>
         </is>
       </c>
-      <c r="AN217" t="inlineStr">
-        <is>
-          <t>10.489</t>
-        </is>
-      </c>
-      <c r="AO217" t="inlineStr">
-        <is>
-          <t>10.3315</t>
-        </is>
+      <c r="AN217" t="n">
+        <v>10.489</v>
+      </c>
+      <c r="AO217" t="n">
+        <v>10.3315</v>
       </c>
       <c r="AP217" t="inlineStr">
         <is>
@@ -84603,15 +83739,11 @@
           <t>10.34</t>
         </is>
       </c>
-      <c r="AN218" t="inlineStr">
-        <is>
-          <t>10.472</t>
-        </is>
-      </c>
-      <c r="AO218" t="inlineStr">
-        <is>
-          <t>10.308625</t>
-        </is>
+      <c r="AN218" t="n">
+        <v>10.472</v>
+      </c>
+      <c r="AO218" t="n">
+        <v>10.308625</v>
       </c>
       <c r="AP218" t="inlineStr">
         <is>
@@ -84990,15 +84122,11 @@
           <t>10.32</t>
         </is>
       </c>
-      <c r="AN219" t="inlineStr">
-        <is>
-          <t>10.464</t>
-        </is>
-      </c>
-      <c r="AO219" t="inlineStr">
-        <is>
-          <t>10.294375</t>
-        </is>
+      <c r="AN219" t="n">
+        <v>10.464</v>
+      </c>
+      <c r="AO219" t="n">
+        <v>10.294375</v>
       </c>
       <c r="AP219" t="inlineStr">
         <is>
@@ -85377,15 +84505,11 @@
           <t>10.3075</t>
         </is>
       </c>
-      <c r="AN220" t="inlineStr">
-        <is>
-          <t>10.462</t>
-        </is>
-      </c>
-      <c r="AO220" t="inlineStr">
-        <is>
-          <t>10.28325</t>
-        </is>
+      <c r="AN220" t="n">
+        <v>10.462</v>
+      </c>
+      <c r="AO220" t="n">
+        <v>10.28325</v>
       </c>
       <c r="AP220" t="inlineStr">
         <is>
@@ -85764,15 +84888,11 @@
           <t>10.2925</t>
         </is>
       </c>
-      <c r="AN221" t="inlineStr">
-        <is>
-          <t>10.458</t>
-        </is>
-      </c>
-      <c r="AO221" t="inlineStr">
-        <is>
-          <t>10.26975</t>
-        </is>
+      <c r="AN221" t="n">
+        <v>10.458</v>
+      </c>
+      <c r="AO221" t="n">
+        <v>10.26975</v>
       </c>
       <c r="AP221" t="inlineStr">
         <is>
@@ -86151,15 +85271,11 @@
           <t>41.44</t>
         </is>
       </c>
-      <c r="AN222" t="inlineStr">
-        <is>
-          <t>40.589</t>
-        </is>
-      </c>
-      <c r="AO222" t="inlineStr">
-        <is>
-          <t>38.3675</t>
-        </is>
+      <c r="AN222" t="n">
+        <v>40.589</v>
+      </c>
+      <c r="AO222" t="n">
+        <v>38.3675</v>
       </c>
       <c r="AP222" t="inlineStr">
         <is>
@@ -86538,15 +85654,11 @@
           <t>41.3375</t>
         </is>
       </c>
-      <c r="AN223" t="inlineStr">
-        <is>
-          <t>40.684</t>
-        </is>
-      </c>
-      <c r="AO223" t="inlineStr">
-        <is>
-          <t>38.204375</t>
-        </is>
+      <c r="AN223" t="n">
+        <v>40.684</v>
+      </c>
+      <c r="AO223" t="n">
+        <v>38.204375</v>
       </c>
       <c r="AP223" t="inlineStr">
         <is>
@@ -86925,15 +86037,11 @@
           <t>41.22000000000001</t>
         </is>
       </c>
-      <c r="AN224" t="inlineStr">
-        <is>
-          <t>40.704</t>
-        </is>
-      </c>
-      <c r="AO224" t="inlineStr">
-        <is>
-          <t>38.0425</t>
-        </is>
+      <c r="AN224" t="n">
+        <v>40.704</v>
+      </c>
+      <c r="AO224" t="n">
+        <v>38.0425</v>
       </c>
       <c r="AP224" t="inlineStr">
         <is>
@@ -87312,15 +86420,11 @@
           <t>41.1675</t>
         </is>
       </c>
-      <c r="AN225" t="inlineStr">
-        <is>
-          <t>40.7</t>
-        </is>
-      </c>
-      <c r="AO225" t="inlineStr">
-        <is>
-          <t>37.88062499999999</t>
-        </is>
+      <c r="AN225" t="n">
+        <v>40.7</v>
+      </c>
+      <c r="AO225" t="n">
+        <v>37.88062499999999</v>
       </c>
       <c r="AP225" t="inlineStr">
         <is>
@@ -87699,15 +86803,11 @@
           <t>40.9875</t>
         </is>
       </c>
-      <c r="AN226" t="inlineStr">
-        <is>
-          <t>40.708</t>
-        </is>
-      </c>
-      <c r="AO226" t="inlineStr">
-        <is>
-          <t>37.7075</t>
-        </is>
+      <c r="AN226" t="n">
+        <v>40.708</v>
+      </c>
+      <c r="AO226" t="n">
+        <v>37.7075</v>
       </c>
       <c r="AP226" t="inlineStr">
         <is>
@@ -88086,15 +87186,11 @@
           <t>40.8275</t>
         </is>
       </c>
-      <c r="AN227" t="inlineStr">
-        <is>
-          <t>40.676</t>
-        </is>
-      </c>
-      <c r="AO227" t="inlineStr">
-        <is>
-          <t>37.515</t>
-        </is>
+      <c r="AN227" t="n">
+        <v>40.676</v>
+      </c>
+      <c r="AO227" t="n">
+        <v>37.515</v>
       </c>
       <c r="AP227" t="inlineStr">
         <is>
@@ -88473,15 +87569,11 @@
           <t>40.685</t>
         </is>
       </c>
-      <c r="AN228" t="inlineStr">
-        <is>
-          <t>40.605</t>
-        </is>
-      </c>
-      <c r="AO228" t="inlineStr">
-        <is>
-          <t>37.31375</t>
-        </is>
+      <c r="AN228" t="n">
+        <v>40.605</v>
+      </c>
+      <c r="AO228" t="n">
+        <v>37.31375</v>
       </c>
       <c r="AP228" t="inlineStr">
         <is>
@@ -88860,15 +87952,11 @@
           <t>40.52999999999999</t>
         </is>
       </c>
-      <c r="AN229" t="inlineStr">
-        <is>
-          <t>40.494</t>
-        </is>
-      </c>
-      <c r="AO229" t="inlineStr">
-        <is>
-          <t>37.135625</t>
-        </is>
+      <c r="AN229" t="n">
+        <v>40.494</v>
+      </c>
+      <c r="AO229" t="n">
+        <v>37.135625</v>
       </c>
       <c r="AP229" t="inlineStr">
         <is>
@@ -89247,15 +88335,11 @@
           <t>40.28</t>
         </is>
       </c>
-      <c r="AN230" t="inlineStr">
-        <is>
-          <t>40.399</t>
-        </is>
-      </c>
-      <c r="AO230" t="inlineStr">
-        <is>
-          <t>36.96875</t>
-        </is>
+      <c r="AN230" t="n">
+        <v>40.399</v>
+      </c>
+      <c r="AO230" t="n">
+        <v>36.96875</v>
       </c>
       <c r="AP230" t="inlineStr">
         <is>
@@ -89634,15 +88718,11 @@
           <t>40.0625</t>
         </is>
       </c>
-      <c r="AN231" t="inlineStr">
-        <is>
-          <t>40.304</t>
-        </is>
-      </c>
-      <c r="AO231" t="inlineStr">
-        <is>
-          <t>36.79125</t>
-        </is>
+      <c r="AN231" t="n">
+        <v>40.304</v>
+      </c>
+      <c r="AO231" t="n">
+        <v>36.79125</v>
       </c>
       <c r="AP231" t="inlineStr">
         <is>
@@ -90021,15 +89101,11 @@
           <t>38.465</t>
         </is>
       </c>
-      <c r="AN232" t="inlineStr">
-        <is>
-          <t>38.521</t>
-        </is>
-      </c>
-      <c r="AO232" t="inlineStr">
-        <is>
-          <t>38.434375</t>
-        </is>
+      <c r="AN232" t="n">
+        <v>38.521</v>
+      </c>
+      <c r="AO232" t="n">
+        <v>38.434375</v>
       </c>
       <c r="AP232" t="inlineStr">
         <is>
@@ -90408,15 +89484,11 @@
           <t>38.4875</t>
         </is>
       </c>
-      <c r="AN233" t="inlineStr">
-        <is>
-          <t>38.567</t>
-        </is>
-      </c>
-      <c r="AO233" t="inlineStr">
-        <is>
-          <t>38.398125</t>
-        </is>
+      <c r="AN233" t="n">
+        <v>38.567</v>
+      </c>
+      <c r="AO233" t="n">
+        <v>38.398125</v>
       </c>
       <c r="AP233" t="inlineStr">
         <is>
@@ -90795,15 +89867,11 @@
           <t>38.4475</t>
         </is>
       </c>
-      <c r="AN234" t="inlineStr">
-        <is>
-          <t>38.578</t>
-        </is>
-      </c>
-      <c r="AO234" t="inlineStr">
-        <is>
-          <t>38.361875</t>
-        </is>
+      <c r="AN234" t="n">
+        <v>38.578</v>
+      </c>
+      <c r="AO234" t="n">
+        <v>38.361875</v>
       </c>
       <c r="AP234" t="inlineStr">
         <is>
@@ -91182,15 +90250,11 @@
           <t>38.435</t>
         </is>
       </c>
-      <c r="AN235" t="inlineStr">
-        <is>
-          <t>38.581</t>
-        </is>
-      </c>
-      <c r="AO235" t="inlineStr">
-        <is>
-          <t>38.32625</t>
-        </is>
+      <c r="AN235" t="n">
+        <v>38.581</v>
+      </c>
+      <c r="AO235" t="n">
+        <v>38.32625</v>
       </c>
       <c r="AP235" t="inlineStr">
         <is>
@@ -91569,15 +90633,11 @@
           <t>38.3525</t>
         </is>
       </c>
-      <c r="AN236" t="inlineStr">
-        <is>
-          <t>38.573</t>
-        </is>
-      </c>
-      <c r="AO236" t="inlineStr">
-        <is>
-          <t>38.28</t>
-        </is>
+      <c r="AN236" t="n">
+        <v>38.573</v>
+      </c>
+      <c r="AO236" t="n">
+        <v>38.28</v>
       </c>
       <c r="AP236" t="inlineStr">
         <is>
@@ -91956,15 +91016,11 @@
           <t>38.2825</t>
         </is>
       </c>
-      <c r="AN237" t="inlineStr">
-        <is>
-          <t>38.567</t>
-        </is>
-      </c>
-      <c r="AO237" t="inlineStr">
-        <is>
-          <t>38.225</t>
-        </is>
+      <c r="AN237" t="n">
+        <v>38.567</v>
+      </c>
+      <c r="AO237" t="n">
+        <v>38.225</v>
       </c>
       <c r="AP237" t="inlineStr">
         <is>
@@ -92343,15 +91399,11 @@
           <t>38.205</t>
         </is>
       </c>
-      <c r="AN238" t="inlineStr">
-        <is>
-          <t>38.532</t>
-        </is>
-      </c>
-      <c r="AO238" t="inlineStr">
-        <is>
-          <t>38.158125</t>
-        </is>
+      <c r="AN238" t="n">
+        <v>38.532</v>
+      </c>
+      <c r="AO238" t="n">
+        <v>38.158125</v>
       </c>
       <c r="AP238" t="inlineStr">
         <is>
@@ -92730,15 +91782,11 @@
           <t>38.17749999999999</t>
         </is>
       </c>
-      <c r="AN239" t="inlineStr">
-        <is>
-          <t>38.504</t>
-        </is>
-      </c>
-      <c r="AO239" t="inlineStr">
-        <is>
-          <t>38.111875</t>
-        </is>
+      <c r="AN239" t="n">
+        <v>38.504</v>
+      </c>
+      <c r="AO239" t="n">
+        <v>38.111875</v>
       </c>
       <c r="AP239" t="inlineStr">
         <is>
@@ -93117,15 +92165,11 @@
           <t>38.1225</t>
         </is>
       </c>
-      <c r="AN240" t="inlineStr">
-        <is>
-          <t>38.499</t>
-        </is>
-      </c>
-      <c r="AO240" t="inlineStr">
-        <is>
-          <t>38.075</t>
-        </is>
+      <c r="AN240" t="n">
+        <v>38.499</v>
+      </c>
+      <c r="AO240" t="n">
+        <v>38.075</v>
       </c>
       <c r="AP240" t="inlineStr">
         <is>
@@ -93504,15 +92548,11 @@
           <t>38.05</t>
         </is>
       </c>
-      <c r="AN241" t="inlineStr">
-        <is>
-          <t>38.49</t>
-        </is>
-      </c>
-      <c r="AO241" t="inlineStr">
-        <is>
-          <t>38.0275</t>
-        </is>
+      <c r="AN241" t="n">
+        <v>38.49</v>
+      </c>
+      <c r="AO241" t="n">
+        <v>38.0275</v>
       </c>
       <c r="AP241" t="inlineStr">
         <is>
